--- a/QuanLyNhaHang.xlsx
+++ b/QuanLyNhaHang.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMINIS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐỒ ÁN IT008\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6A156B-0305-42F7-A0FF-292DDC3BC414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8427B842-9D83-4EE4-AC25-E11D34039BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="KhachHang" sheetId="1" r:id="rId1"/>
@@ -31,14 +31,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="636">
   <si>
     <t>MaKH</t>
   </si>
   <si>
-    <t>SĐT</t>
-  </si>
-  <si>
     <t>NgayĐK</t>
   </si>
   <si>
@@ -96,88 +93,58 @@
     <t>MaCombo</t>
   </si>
   <si>
-    <t>KH01</t>
-  </si>
-  <si>
     <t>0905123456</t>
   </si>
   <si>
     <t>2023-01-15</t>
   </si>
   <si>
-    <t>KH02</t>
-  </si>
-  <si>
     <t>0912345678</t>
   </si>
   <si>
     <t>2023-02-20</t>
   </si>
   <si>
-    <t>KH03</t>
-  </si>
-  <si>
     <t>0987654321</t>
   </si>
   <si>
     <t>2023-03-05</t>
   </si>
   <si>
-    <t>KH04</t>
-  </si>
-  <si>
     <t>0933123456</t>
   </si>
   <si>
     <t>2023-03-25</t>
   </si>
   <si>
-    <t>KH05</t>
-  </si>
-  <si>
     <t>0976543210</t>
   </si>
   <si>
     <t>2023-04-10</t>
   </si>
   <si>
-    <t>KH06</t>
-  </si>
-  <si>
     <t>0909988776</t>
   </si>
   <si>
     <t>2023-05-01</t>
   </si>
   <si>
-    <t>KH07</t>
-  </si>
-  <si>
     <t>0911002233</t>
   </si>
   <si>
     <t>2023-06-12</t>
   </si>
   <si>
-    <t>KH08</t>
-  </si>
-  <si>
     <t>0933444555</t>
   </si>
   <si>
     <t>2023-07-08</t>
   </si>
   <si>
-    <t>KH09</t>
-  </si>
-  <si>
     <t>0988777666</t>
   </si>
   <si>
     <t>2023-08-30</t>
-  </si>
-  <si>
-    <t>KH10</t>
   </si>
   <si>
     <t>0909111222</t>
@@ -2106,7 +2073,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2173,6 +2140,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2491,16 +2464,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BEB041C-81B4-439A-B341-2A7E649D56EE}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2510,147 +2482,114 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="C3" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" s="4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C5" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="4">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="C6" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C7" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="C9" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C11" s="4">
         <v>20</v>
       </c>
     </row>
@@ -2669,123 +2608,123 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B2" s="6">
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B3" s="6">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B4" s="6">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B5" s="6">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B6" s="6">
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B7" s="6">
         <v>10</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B8" s="6">
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B9" s="6">
         <v>4</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B10" s="6">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B11" s="6">
         <v>12</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2805,350 +2744,350 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3171,2813 +3110,2813 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F2" s="6">
         <v>75000</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F3" s="6">
         <v>125000</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F4" s="6">
         <v>65000</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F5" s="6">
         <v>80000</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F6" s="6">
         <v>95000</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F7" s="6">
         <v>90000</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F8" s="6">
         <v>145000</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F9" s="6">
         <v>120000</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F10" s="6">
         <v>135000</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F11" s="6">
         <v>100000</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F12" s="6">
         <v>150000</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F13" s="6">
         <v>100000</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F14" s="6">
         <v>130000</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F15" s="6">
         <v>90000</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F16" s="6">
         <v>120000</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F17" s="6">
         <v>95000</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F18" s="6">
         <v>110000</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F19" s="6">
         <v>95000</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F20" s="6">
         <v>100000</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F21" s="6">
         <v>85000</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>227</v>
-      </c>
       <c r="E22" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F22" s="7">
         <v>135000</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>228</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F23" s="7">
         <v>220000</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>229</v>
-      </c>
       <c r="E24" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F24" s="7">
         <v>120000</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>230</v>
-      </c>
       <c r="E25" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F25" s="7">
         <v>140000</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>231</v>
-      </c>
       <c r="E26" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F26" s="7">
         <v>180000</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>232</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F27" s="7">
         <v>210000</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>233</v>
-      </c>
       <c r="E28" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F28" s="7">
         <v>190000</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F29" s="7">
         <v>175000</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F30" s="7">
         <v>200000</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C31" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="E31" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F31" s="7">
         <v>110000</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F32" s="7">
         <v>95000</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F33" s="7">
         <v>85000</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F34" s="7">
         <v>90000</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F35" s="7">
         <v>130000</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F36" s="7">
         <v>100000</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F37" s="7">
         <v>250000</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F38" s="7">
         <v>270000</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F39" s="7">
         <v>230000</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F40" s="7">
         <v>290000</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F41" s="7">
         <v>280000</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F42" s="7">
         <v>240000</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F43" s="7">
         <v>300000</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F44" s="7">
         <v>190000</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F45" s="7">
         <v>195000</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F46" s="7">
         <v>350000</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F47" s="7">
         <v>330000</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F48" s="7">
         <v>379000</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F49" s="16">
         <v>500000</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F50" s="17">
         <v>79000</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F51" s="17">
         <v>69000</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F52" s="17">
         <v>59000</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F53" s="17">
         <v>69000</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F54" s="14">
         <v>55000</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F55" s="17">
         <v>45000</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F56" s="17">
         <v>59000</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F57" s="17">
         <v>65000</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F58" s="17">
         <v>79000</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F59" s="17">
         <v>69000</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F60" s="14">
         <v>65000</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F61" s="17">
         <v>45000</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F62" s="17">
         <v>69000</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F63" s="17">
         <v>55000</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F64" s="14">
         <v>49000</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F65" s="6">
         <v>60000</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F66" s="6">
         <v>65000</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F67" s="6">
         <v>45000</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F68" s="6">
         <v>55000</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F69" s="6">
         <v>40000</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F70" s="6">
         <v>45000</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F71" s="6">
         <v>38000</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F72" s="6">
         <v>20000</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F73" s="6">
         <v>30000</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F74" s="6">
         <v>30000</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F75" s="6">
         <v>30000</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F76" s="6">
         <v>30000</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F77" s="6">
         <v>160000</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F78" s="6">
         <v>180000</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F79" s="6">
         <v>170000</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F80" s="6">
         <v>220000</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F81" s="6">
         <v>100000</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F82" s="6">
         <v>90000</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F83" s="6">
         <v>85000</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F84" s="6">
         <v>130000</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F85" s="6">
         <v>125000</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F86" s="6">
         <v>200000</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F87" s="6">
         <v>30000</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F88" s="18">
         <v>35000</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F89" s="6">
         <v>70000</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="D90" s="18" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F90" s="6">
         <v>25000</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F91" s="6">
         <v>70000</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F92" s="6">
         <v>85000</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="D93" s="18" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F93" s="18">
         <v>60000</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="B94" s="20" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F94" s="9">
         <v>45000</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F95" s="6">
         <v>50000</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="D96" s="18" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F96" s="6">
         <v>65000</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F97" s="6">
         <v>50000</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F98" s="6">
         <v>55000</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F99" s="6">
         <v>65000</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F100" s="6">
         <v>85000</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F101" s="17">
         <v>5000</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F102" s="17">
         <v>8000</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F103" s="14">
         <v>15000</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F104" s="14">
         <v>12000</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F105" s="14">
         <v>10000</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F106" s="14">
         <v>10000</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F107" s="14">
         <v>8000</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F108" s="17">
         <v>12000</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F109" s="17">
         <v>10000</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F110" s="17">
         <v>10000</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F111" s="17">
         <v>8000</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F112" s="17">
         <v>12000</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="D113" s="18" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F113" s="17">
         <v>12000</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="C114" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="B114" s="19" t="s">
-        <v>532</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>570</v>
-      </c>
       <c r="D114" s="18" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F114" s="17">
         <v>15000</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="C115" s="6"/>
       <c r="D115" s="18" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F115" s="6">
         <v>503000</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="6" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F116" s="6">
         <v>503000</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="C117" s="6"/>
       <c r="D117" s="6" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F117" s="6">
         <v>665000</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="6" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F118" s="6">
         <v>840000</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="C119" s="6"/>
       <c r="D119" s="6" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F119" s="6">
         <v>970000</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="6" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F120" s="6">
         <v>927000</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="C121" s="6"/>
       <c r="D121" s="6" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F121" s="6">
         <v>1537000</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="6" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F122" s="6">
         <v>1470000</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="C123" s="6"/>
       <c r="D123" s="6" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F123" s="6">
         <v>1912000</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -5997,6 +5936,7 @@
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
     <col min="4" max="4" width="14.88671875" customWidth="1"/>
     <col min="5" max="5" width="19.109375" customWidth="1"/>
     <col min="6" max="6" width="20.88671875" customWidth="1"/>
@@ -6010,57 +5950,57 @@
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>32</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G2" s="7">
         <v>585000</v>
@@ -6072,30 +6012,30 @@
         <v>580745</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>27</v>
+        <v>40</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7">
         <v>270000</v>
@@ -6107,30 +6047,30 @@
         <v>250000</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>27</v>
+        <v>42</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G4" s="7">
         <v>890000</v>
@@ -6142,30 +6082,30 @@
         <v>890000</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>30</v>
+        <v>50</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G5" s="7">
         <v>230000</v>
@@ -6177,30 +6117,30 @@
         <v>230000</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>33</v>
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G6" s="7">
         <v>1070000</v>
@@ -6212,30 +6152,30 @@
         <v>1060500</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>24</v>
+        <v>49</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G7" s="7">
         <v>215000</v>
@@ -6247,30 +6187,30 @@
         <v>215000</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G8" s="7">
         <v>1680000</v>
@@ -6282,30 +6222,30 @@
         <v>1680000</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>24</v>
+        <v>40</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G9" s="7">
         <v>915000</v>
@@ -6317,30 +6257,30 @@
         <v>912000</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G10" s="7">
         <v>260000</v>
@@ -6352,30 +6292,30 @@
         <v>248000</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>24</v>
+        <v>50</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G11" s="7">
         <v>465000</v>
@@ -6387,10 +6327,10 @@
         <v>456000</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -6411,27 +6351,27 @@
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C2" s="6">
         <v>2</v>
@@ -6445,10 +6385,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -6462,10 +6402,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C4" s="6">
         <v>2</v>
@@ -6479,10 +6419,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
@@ -6496,10 +6436,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -6513,10 +6453,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -6530,10 +6470,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C8" s="6">
         <v>2</v>
@@ -6547,10 +6487,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -6564,10 +6504,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C10" s="6">
         <v>3</v>
@@ -6581,10 +6521,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -6598,10 +6538,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -6615,10 +6555,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C13" s="6">
         <v>2</v>
@@ -6632,10 +6572,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C14" s="6">
         <v>4</v>
@@ -6649,10 +6589,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -6666,10 +6606,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
@@ -6683,10 +6623,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="C17" s="6">
         <v>2</v>
@@ -6700,10 +6640,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
@@ -6717,10 +6657,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="C19" s="6">
         <v>1</v>
@@ -6734,10 +6674,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C20" s="6">
         <v>2</v>
@@ -6751,10 +6691,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C21" s="6">
         <v>2</v>
@@ -6768,10 +6708,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
@@ -6785,10 +6725,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
@@ -6802,10 +6742,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C24" s="6">
         <v>1</v>
@@ -6834,21 +6774,21 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
@@ -6856,10 +6796,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -6867,10 +6807,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
@@ -6878,10 +6818,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
@@ -6889,10 +6829,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -6900,10 +6840,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -6911,10 +6851,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
@@ -6922,10 +6862,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -6933,10 +6873,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
@@ -6944,10 +6884,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -6955,10 +6895,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -6966,10 +6906,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -6977,10 +6917,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C14" s="6">
         <v>1</v>
@@ -6988,10 +6928,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -6999,10 +6939,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
@@ -7010,10 +6950,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C17" s="6">
         <v>1</v>
@@ -7021,10 +6961,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
@@ -7032,10 +6972,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C19" s="6">
         <v>2</v>
@@ -7043,10 +6983,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
@@ -7054,10 +6994,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C21" s="6">
         <v>1</v>
@@ -7065,10 +7005,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
@@ -7076,10 +7016,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
@@ -7087,10 +7027,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="C24" s="6">
         <v>1</v>
@@ -7098,10 +7038,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="C25" s="6">
         <v>2</v>
@@ -7109,10 +7049,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C26" s="6">
         <v>1</v>
@@ -7120,10 +7060,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="C27" s="6">
         <v>1</v>
@@ -7131,10 +7071,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="C28" s="6">
         <v>1</v>
@@ -7142,10 +7082,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C29" s="6">
         <v>1</v>
@@ -7153,10 +7093,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C30" s="6">
         <v>1</v>
@@ -7164,10 +7104,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="C31" s="6">
         <v>2</v>
@@ -7175,10 +7115,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C32" s="6">
         <v>2</v>
@@ -7186,10 +7126,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C33" s="6">
         <v>2</v>
@@ -7197,10 +7137,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C34" s="6">
         <v>1</v>
@@ -7208,10 +7148,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C35" s="6">
         <v>2</v>
@@ -7219,10 +7159,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C36" s="6">
         <v>1</v>
@@ -7230,10 +7170,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C37" s="6">
         <v>1</v>
@@ -7241,10 +7181,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C38" s="6">
         <v>2</v>
@@ -7252,10 +7192,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="C39" s="6">
         <v>1</v>
@@ -7263,10 +7203,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C40" s="6">
         <v>2</v>
@@ -7274,10 +7214,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="C41" s="6">
         <v>2</v>
@@ -7285,10 +7225,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C42" s="6">
         <v>2</v>
@@ -7296,10 +7236,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="C43" s="6">
         <v>1</v>
@@ -7307,10 +7247,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C44" s="6">
         <v>1</v>
@@ -7318,10 +7258,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="C45" s="6">
         <v>1</v>
@@ -7329,10 +7269,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="C46" s="6">
         <v>2</v>
@@ -7340,10 +7280,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="C47" s="6">
         <v>1</v>
@@ -7351,10 +7291,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C48" s="6">
         <v>2</v>
@@ -7362,10 +7302,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C49" s="6">
         <v>2</v>
@@ -7373,10 +7313,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -7384,10 +7324,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C51" s="6">
         <v>1</v>
@@ -7395,10 +7335,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C52" s="6">
         <v>2</v>
@@ -7406,10 +7346,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C53" s="6">
         <v>1</v>
@@ -7417,10 +7357,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="C54" s="6">
         <v>2</v>

--- a/QuanLyNhaHang.xlsx
+++ b/QuanLyNhaHang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐỒ ÁN IT008\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8427B842-9D83-4EE4-AC25-E11D34039BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6BF099-33CA-475E-AD91-4975AA31868A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="KhachHang" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="644">
   <si>
     <t>MaKH</t>
   </si>
@@ -1939,6 +1939,30 @@
   </si>
   <si>
     <t>GioRa</t>
+  </si>
+  <si>
+    <t>combo_ca_nhan_1.jpg</t>
+  </si>
+  <si>
+    <t>combo_ca_nhan_2.jpg</t>
+  </si>
+  <si>
+    <t>combo_ca_nhan_3.jpg</t>
+  </si>
+  <si>
+    <t>combo_nhom_lon_1.jpg</t>
+  </si>
+  <si>
+    <t>combo_nhom_lon_2.jpg</t>
+  </si>
+  <si>
+    <t>combo_nhom_lon_3.jpg</t>
+  </si>
+  <si>
+    <t>combo_nhom_nho_3.jpg</t>
+  </si>
+  <si>
+    <t>combo_nhom_nho_2.jpg</t>
   </si>
 </sst>
 </file>
@@ -5737,7 +5761,9 @@
       <c r="B115" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="C115" s="6"/>
+      <c r="C115" s="6" t="s">
+        <v>636</v>
+      </c>
       <c r="D115" s="18" t="s">
         <v>586</v>
       </c>
@@ -5758,7 +5784,9 @@
       <c r="B116" s="19" t="s">
         <v>580</v>
       </c>
-      <c r="C116" s="6"/>
+      <c r="C116" s="6" t="s">
+        <v>637</v>
+      </c>
       <c r="D116" s="6" t="s">
         <v>586</v>
       </c>
@@ -5779,7 +5807,9 @@
       <c r="B117" s="6" t="s">
         <v>581</v>
       </c>
-      <c r="C117" s="6"/>
+      <c r="C117" s="6" t="s">
+        <v>638</v>
+      </c>
       <c r="D117" s="6" t="s">
         <v>586</v>
       </c>
@@ -5821,7 +5851,9 @@
       <c r="B119" s="19" t="s">
         <v>582</v>
       </c>
-      <c r="C119" s="6"/>
+      <c r="C119" s="6" t="s">
+        <v>643</v>
+      </c>
       <c r="D119" s="6" t="s">
         <v>587</v>
       </c>
@@ -5842,7 +5874,9 @@
       <c r="B120" s="19" t="s">
         <v>583</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="6" t="s">
+        <v>642</v>
+      </c>
       <c r="D120" s="6" t="s">
         <v>587</v>
       </c>
@@ -5863,7 +5897,9 @@
       <c r="B121" s="19" t="s">
         <v>579</v>
       </c>
-      <c r="C121" s="6"/>
+      <c r="C121" s="6" t="s">
+        <v>639</v>
+      </c>
       <c r="D121" s="6" t="s">
         <v>597</v>
       </c>
@@ -5884,7 +5920,9 @@
       <c r="B122" s="19" t="s">
         <v>584</v>
       </c>
-      <c r="C122" s="6"/>
+      <c r="C122" s="6" t="s">
+        <v>640</v>
+      </c>
       <c r="D122" s="6" t="s">
         <v>597</v>
       </c>
@@ -5905,7 +5943,9 @@
       <c r="B123" s="19" t="s">
         <v>585</v>
       </c>
-      <c r="C123" s="6"/>
+      <c r="C123" s="6" t="s">
+        <v>641</v>
+      </c>
       <c r="D123" s="6" t="s">
         <v>597</v>
       </c>

--- a/QuanLyNhaHang.xlsx
+++ b/QuanLyNhaHang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐỒ ÁN IT008\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6BF099-33CA-475E-AD91-4975AA31868A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB37854-BB51-41A3-8294-06F579A21DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="KhachHang" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="645">
   <si>
     <t>MaKH</t>
   </si>
@@ -1963,6 +1963,9 @@
   </si>
   <si>
     <t>combo_nhom_nho_2.jpg</t>
+  </si>
+  <si>
+    <t>combo_nhom_nho_1</t>
   </si>
 </sst>
 </file>
@@ -5830,7 +5833,9 @@
       <c r="B118" s="19" t="s">
         <v>578</v>
       </c>
-      <c r="C118" s="6"/>
+      <c r="C118" s="6" t="s">
+        <v>644</v>
+      </c>
       <c r="D118" s="6" t="s">
         <v>587</v>
       </c>

--- a/QuanLyNhaHang.xlsx
+++ b/QuanLyNhaHang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐỒ ÁN IT008\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB37854-BB51-41A3-8294-06F579A21DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B78C21-8F41-4BC3-B83C-F8256B7C54E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="KhachHang" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="656">
   <si>
     <t>MaKH</t>
   </si>
@@ -186,9 +186,6 @@
     <t>B10</t>
   </si>
   <si>
-    <t>2023-07-01</t>
-  </si>
-  <si>
     <t>Chưa thanh toán</t>
   </si>
   <si>
@@ -198,39 +195,15 @@
     <t>Chờ xác nhận</t>
   </si>
   <si>
-    <t>2023-07-15</t>
-  </si>
-  <si>
     <t>Đã thanh toán</t>
   </si>
   <si>
     <t>Khách đặt bàn trước</t>
   </si>
   <si>
-    <t>2023-07-22</t>
-  </si>
-  <si>
-    <t>2023-07-29</t>
-  </si>
-  <si>
     <t>Giảm giá 10%</t>
   </si>
   <si>
-    <t>2023-08-05</t>
-  </si>
-  <si>
-    <t>2023-08-12</t>
-  </si>
-  <si>
-    <t>2023-08-19</t>
-  </si>
-  <si>
-    <t>2023-08-26</t>
-  </si>
-  <si>
-    <t>2023-09-02</t>
-  </si>
-  <si>
     <t>L01</t>
   </si>
   <si>
@@ -1966,14 +1939,75 @@
   </si>
   <si>
     <t>combo_nhom_nho_1</t>
+  </si>
+  <si>
+    <t>HD011</t>
+  </si>
+  <si>
+    <t>HD012</t>
+  </si>
+  <si>
+    <t>HD013</t>
+  </si>
+  <si>
+    <t>HD014</t>
+  </si>
+  <si>
+    <t>HD015</t>
+  </si>
+  <si>
+    <t>HD016</t>
+  </si>
+  <si>
+    <t>HD017</t>
+  </si>
+  <si>
+    <t>HD018</t>
+  </si>
+  <si>
+    <t>HD019</t>
+  </si>
+  <si>
+    <t>HD020</t>
+  </si>
+  <si>
+    <t>HD021</t>
+  </si>
+  <si>
+    <t>HD022</t>
+  </si>
+  <si>
+    <t>HD023</t>
+  </si>
+  <si>
+    <t>HD024</t>
+  </si>
+  <si>
+    <t>HD025</t>
+  </si>
+  <si>
+    <t>HD026</t>
+  </si>
+  <si>
+    <t>HD027</t>
+  </si>
+  <si>
+    <t>HD028</t>
+  </si>
+  <si>
+    <t>HD029</t>
+  </si>
+  <si>
+    <t>HD030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-1000000]h:mm:ss;@"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -2100,7 +2134,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2175,6 +2209,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2782,339 +2823,339 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C3" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3160,2808 +3201,2808 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F2" s="6">
         <v>75000</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F3" s="6">
         <v>125000</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F4" s="6">
         <v>65000</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F5" s="6">
         <v>80000</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F6" s="6">
         <v>95000</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F7" s="6">
         <v>90000</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F8" s="6">
         <v>145000</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F9" s="6">
         <v>120000</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F10" s="6">
         <v>135000</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F11" s="6">
         <v>100000</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F12" s="6">
         <v>150000</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F13" s="6">
         <v>100000</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F14" s="6">
         <v>130000</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F15" s="6">
         <v>90000</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F16" s="6">
         <v>120000</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F17" s="6">
         <v>95000</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F18" s="6">
         <v>110000</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F19" s="6">
         <v>95000</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F20" s="6">
         <v>100000</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F21" s="6">
         <v>85000</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F22" s="7">
         <v>135000</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F23" s="7">
         <v>220000</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F24" s="7">
         <v>120000</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F25" s="7">
         <v>140000</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F26" s="7">
         <v>180000</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F27" s="7">
         <v>210000</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F28" s="7">
         <v>190000</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F29" s="7">
         <v>175000</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F30" s="7">
         <v>200000</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F31" s="7">
         <v>110000</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F32" s="7">
         <v>95000</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F33" s="7">
         <v>85000</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F34" s="7">
         <v>90000</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F35" s="7">
         <v>130000</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F36" s="7">
         <v>100000</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F37" s="7">
         <v>250000</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F38" s="7">
         <v>270000</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F39" s="7">
         <v>230000</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F40" s="7">
         <v>290000</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F41" s="7">
         <v>280000</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F42" s="7">
         <v>240000</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F43" s="7">
         <v>300000</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F44" s="7">
         <v>190000</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F45" s="7">
         <v>195000</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F46" s="7">
         <v>350000</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F47" s="7">
         <v>330000</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F48" s="7">
         <v>379000</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F49" s="16">
         <v>500000</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F50" s="17">
         <v>79000</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F51" s="17">
         <v>69000</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F52" s="17">
         <v>59000</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F53" s="17">
         <v>69000</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F54" s="14">
         <v>55000</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F55" s="17">
         <v>45000</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F56" s="17">
         <v>59000</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F57" s="17">
         <v>65000</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F58" s="17">
         <v>79000</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F59" s="17">
         <v>69000</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F60" s="14">
         <v>65000</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F61" s="17">
         <v>45000</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F62" s="17">
         <v>69000</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F63" s="17">
         <v>55000</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F64" s="14">
         <v>49000</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F65" s="6">
         <v>60000</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F66" s="6">
         <v>65000</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F67" s="6">
         <v>45000</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F68" s="6">
         <v>55000</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F69" s="6">
         <v>40000</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F70" s="6">
         <v>45000</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F71" s="6">
         <v>38000</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F72" s="6">
         <v>20000</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F73" s="6">
         <v>30000</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F74" s="6">
         <v>30000</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F75" s="6">
         <v>30000</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F76" s="6">
         <v>30000</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F77" s="6">
         <v>160000</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F78" s="6">
         <v>180000</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F79" s="6">
         <v>170000</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F80" s="6">
         <v>220000</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F81" s="6">
         <v>100000</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F82" s="6">
         <v>90000</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F83" s="6">
         <v>85000</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F84" s="6">
         <v>130000</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F85" s="6">
         <v>125000</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F86" s="6">
         <v>200000</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F87" s="6">
         <v>30000</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F88" s="18">
         <v>35000</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F89" s="6">
         <v>70000</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="B90" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="D90" s="18" t="s">
         <v>469</v>
       </c>
-      <c r="C90" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="D90" s="18" t="s">
-        <v>478</v>
-      </c>
       <c r="E90" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F90" s="6">
         <v>25000</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F91" s="6">
         <v>70000</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F92" s="6">
         <v>85000</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="D93" s="18" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F93" s="18">
         <v>60000</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B94" s="20" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F94" s="9">
         <v>45000</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F95" s="6">
         <v>50000</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="D96" s="18" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F96" s="6">
         <v>65000</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F97" s="6">
         <v>50000</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="B98" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="D98" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="C98" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>500</v>
-      </c>
       <c r="E98" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F98" s="6">
         <v>55000</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F99" s="6">
         <v>65000</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F100" s="6">
         <v>85000</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F101" s="17">
         <v>5000</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F102" s="17">
         <v>8000</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F103" s="14">
         <v>15000</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F104" s="14">
         <v>12000</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F105" s="14">
         <v>10000</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F106" s="14">
         <v>10000</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F107" s="14">
         <v>8000</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F108" s="17">
         <v>12000</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F109" s="17">
         <v>10000</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F110" s="17">
         <v>10000</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F111" s="17">
         <v>8000</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F112" s="17">
         <v>12000</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="D113" s="18" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F113" s="17">
         <v>12000</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="D114" s="18" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F114" s="17">
         <v>15000</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B115" s="18" t="s">
+        <v>568</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="D115" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="C115" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="D115" s="18" t="s">
-        <v>586</v>
-      </c>
       <c r="E115" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F115" s="6">
         <v>503000</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F116" s="6">
         <v>503000</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F117" s="6">
         <v>665000</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="B118" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="D118" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>644</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>587</v>
-      </c>
       <c r="E118" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F118" s="6">
         <v>840000</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F119" s="6">
         <v>970000</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F120" s="6">
         <v>927000</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F121" s="6">
         <v>1537000</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F122" s="6">
         <v>1470000</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F123" s="6">
         <v>1912000</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -5978,13 +6019,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C67116-806E-4F8F-AE20-17E61EFDB4E5}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.88671875" customWidth="1"/>
     <col min="4" max="4" width="14.88671875" customWidth="1"/>
     <col min="5" max="5" width="19.109375" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" customWidth="1"/>
+    <col min="6" max="6" width="20.88671875" style="28" customWidth="1"/>
     <col min="7" max="7" width="16.21875" customWidth="1"/>
     <col min="8" max="8" width="14.44140625" customWidth="1"/>
     <col min="9" max="9" width="20.6640625" customWidth="1"/>
@@ -6004,19 +6045,19 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="F1" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="F1" s="26" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
@@ -6030,7 +6071,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>48</v>
@@ -6039,13 +6080,13 @@
         <v>32</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>51</v>
+        <v>594</v>
+      </c>
+      <c r="F2" s="27">
+        <v>45953</v>
       </c>
       <c r="G2" s="7">
         <v>585000</v>
@@ -6057,15 +6098,15 @@
         <v>580745</v>
       </c>
       <c r="J2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>40</v>
@@ -6074,13 +6115,13 @@
         <v>24</v>
       </c>
       <c r="D3" s="22" t="s">
+        <v>595</v>
+      </c>
+      <c r="E3" s="22" t="s">
         <v>604</v>
       </c>
-      <c r="E3" s="22" t="s">
-        <v>613</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>35</v>
+      <c r="F3" s="27">
+        <v>45953</v>
       </c>
       <c r="G3" s="7">
         <v>270000</v>
@@ -6092,15 +6133,15 @@
         <v>250000</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>42</v>
@@ -6109,13 +6150,13 @@
         <v>24</v>
       </c>
       <c r="D4" s="22" t="s">
+        <v>596</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>605</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>614</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>55</v>
+      <c r="F4" s="27">
+        <v>45953</v>
       </c>
       <c r="G4" s="7">
         <v>890000</v>
@@ -6127,15 +6168,15 @@
         <v>890000</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>50</v>
@@ -6144,13 +6185,13 @@
         <v>26</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>597</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>606</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>615</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>58</v>
+      <c r="F5" s="27">
+        <v>45954</v>
       </c>
       <c r="G5" s="7">
         <v>230000</v>
@@ -6162,15 +6203,15 @@
         <v>230000</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>44</v>
@@ -6179,13 +6220,13 @@
         <v>28</v>
       </c>
       <c r="D6" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>607</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>616</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>59</v>
+      <c r="F6" s="27">
+        <v>45954</v>
       </c>
       <c r="G6" s="7">
         <v>1070000</v>
@@ -6197,15 +6238,15 @@
         <v>1060500</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>49</v>
@@ -6214,13 +6255,13 @@
         <v>22</v>
       </c>
       <c r="D7" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>608</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>617</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>61</v>
+      <c r="F7" s="27">
+        <v>45954</v>
       </c>
       <c r="G7" s="7">
         <v>215000</v>
@@ -6232,15 +6273,15 @@
         <v>215000</v>
       </c>
       <c r="J7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>44</v>
@@ -6249,13 +6290,13 @@
         <v>34</v>
       </c>
       <c r="D8" s="22" t="s">
+        <v>600</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>609</v>
       </c>
-      <c r="E8" s="22" t="s">
-        <v>618</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>62</v>
+      <c r="F8" s="27">
+        <v>45954</v>
       </c>
       <c r="G8" s="7">
         <v>1680000</v>
@@ -6267,15 +6308,15 @@
         <v>1680000</v>
       </c>
       <c r="J8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>40</v>
@@ -6284,13 +6325,13 @@
         <v>22</v>
       </c>
       <c r="D9" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>610</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>619</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>63</v>
+      <c r="F9" s="27">
+        <v>45954</v>
       </c>
       <c r="G9" s="7">
         <v>915000</v>
@@ -6302,15 +6343,15 @@
         <v>912000</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>49</v>
@@ -6319,13 +6360,13 @@
         <v>34</v>
       </c>
       <c r="D10" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>611</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>620</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>64</v>
+      <c r="F10" s="27">
+        <v>45955</v>
       </c>
       <c r="G10" s="7">
         <v>260000</v>
@@ -6337,15 +6378,15 @@
         <v>248000</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>50</v>
@@ -6354,13 +6395,13 @@
         <v>22</v>
       </c>
       <c r="D11" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="E11" s="22" t="s">
         <v>612</v>
       </c>
-      <c r="E11" s="22" t="s">
-        <v>621</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>65</v>
+      <c r="F11" s="27">
+        <v>45955</v>
       </c>
       <c r="G11" s="7">
         <v>465000</v>
@@ -6372,10 +6413,710 @@
         <v>456000</v>
       </c>
       <c r="J11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>593</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>594</v>
+      </c>
+      <c r="F12" s="27">
+        <v>45962</v>
+      </c>
+      <c r="G12" s="7">
+        <v>585000</v>
+      </c>
+      <c r="H12" s="7">
+        <v>4255</v>
+      </c>
+      <c r="I12" s="7">
+        <v>580745</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="7" t="s">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>595</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>604</v>
+      </c>
+      <c r="F13" s="27">
+        <v>45962</v>
+      </c>
+      <c r="G13" s="7">
+        <v>270000</v>
+      </c>
+      <c r="H13" s="7">
+        <v>15000</v>
+      </c>
+      <c r="I13" s="7">
+        <v>250000</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>596</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>605</v>
+      </c>
+      <c r="F14" s="27">
+        <v>45966</v>
+      </c>
+      <c r="G14" s="7">
+        <v>890000</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7">
+        <v>890000</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>54</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>597</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>606</v>
+      </c>
+      <c r="F15" s="27">
+        <v>45966</v>
+      </c>
+      <c r="G15" s="7">
+        <v>230000</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0</v>
+      </c>
+      <c r="I15" s="7">
+        <v>230000</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>607</v>
+      </c>
+      <c r="F16" s="27">
+        <v>45966</v>
+      </c>
+      <c r="G16" s="7">
+        <v>1070000</v>
+      </c>
+      <c r="H16" s="7">
+        <v>9500</v>
+      </c>
+      <c r="I16" s="7">
+        <v>1060500</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="F17" s="27">
+        <v>45967</v>
+      </c>
+      <c r="G17" s="7">
+        <v>215000</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7">
+        <v>215000</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>600</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="F18" s="27">
+        <v>45967</v>
+      </c>
+      <c r="G18" s="7">
+        <v>1680000</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6">
+        <v>1680000</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>610</v>
+      </c>
+      <c r="F19" s="27">
+        <v>45971</v>
+      </c>
+      <c r="G19" s="7">
+        <v>915000</v>
+      </c>
+      <c r="H19" s="7">
+        <v>3000</v>
+      </c>
+      <c r="I19" s="7">
+        <v>912000</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>611</v>
+      </c>
+      <c r="F20" s="27">
+        <v>45971</v>
+      </c>
+      <c r="G20" s="7">
+        <v>260000</v>
+      </c>
+      <c r="H20" s="7">
+        <v>12000</v>
+      </c>
+      <c r="I20" s="7">
+        <v>248000</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>612</v>
+      </c>
+      <c r="F21" s="27">
+        <v>45971</v>
+      </c>
+      <c r="G21" s="7">
+        <v>465000</v>
+      </c>
+      <c r="H21" s="7">
+        <v>9000</v>
+      </c>
+      <c r="I21" s="7">
+        <v>456000</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>593</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>594</v>
+      </c>
+      <c r="F22" s="27">
+        <v>46002</v>
+      </c>
+      <c r="G22" s="7">
+        <v>585000</v>
+      </c>
+      <c r="H22" s="7">
+        <v>4255</v>
+      </c>
+      <c r="I22" s="7">
+        <v>580745</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>595</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>604</v>
+      </c>
+      <c r="F23" s="27">
+        <v>46002</v>
+      </c>
+      <c r="G23" s="7">
+        <v>270000</v>
+      </c>
+      <c r="H23" s="7">
+        <v>15000</v>
+      </c>
+      <c r="I23" s="7">
+        <v>250000</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>596</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>605</v>
+      </c>
+      <c r="F24" s="27">
+        <v>46002</v>
+      </c>
+      <c r="G24" s="7">
+        <v>890000</v>
+      </c>
+      <c r="H24" s="7">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7">
+        <v>890000</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>597</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>606</v>
+      </c>
+      <c r="F25" s="27">
+        <v>46002</v>
+      </c>
+      <c r="G25" s="7">
+        <v>230000</v>
+      </c>
+      <c r="H25" s="7">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7">
+        <v>230000</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>607</v>
+      </c>
+      <c r="F26" s="27">
+        <v>46005</v>
+      </c>
+      <c r="G26" s="7">
+        <v>1070000</v>
+      </c>
+      <c r="H26" s="7">
+        <v>9500</v>
+      </c>
+      <c r="I26" s="7">
+        <v>1060500</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="F27" s="27">
+        <v>46005</v>
+      </c>
+      <c r="G27" s="7">
+        <v>215000</v>
+      </c>
+      <c r="H27" s="7">
+        <v>0</v>
+      </c>
+      <c r="I27" s="7">
+        <v>215000</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>600</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="F28" s="27">
+        <v>46005</v>
+      </c>
+      <c r="G28" s="7">
+        <v>1680000</v>
+      </c>
+      <c r="H28" s="7">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6">
+        <v>1680000</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>610</v>
+      </c>
+      <c r="F29" s="27">
+        <v>46015</v>
+      </c>
+      <c r="G29" s="7">
+        <v>915000</v>
+      </c>
+      <c r="H29" s="7">
+        <v>3000</v>
+      </c>
+      <c r="I29" s="7">
+        <v>912000</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>611</v>
+      </c>
+      <c r="F30" s="27">
+        <v>46016</v>
+      </c>
+      <c r="G30" s="7">
+        <v>260000</v>
+      </c>
+      <c r="H30" s="7">
+        <v>12000</v>
+      </c>
+      <c r="I30" s="7">
+        <v>248000</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>612</v>
+      </c>
+      <c r="F31" s="27">
+        <v>46016</v>
+      </c>
+      <c r="G31" s="7">
+        <v>465000</v>
+      </c>
+      <c r="H31" s="7">
+        <v>9000</v>
+      </c>
+      <c r="I31" s="7">
+        <v>456000</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -6387,7 +7128,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FC086EC-74CB-4344-93F9-D1F3265B5BB1}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="4" width="9.88671875" customWidth="1"/>
@@ -6405,7 +7146,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6413,10 +7154,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C2" s="6">
         <v>2</v>
@@ -6430,10 +7171,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -6447,10 +7188,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C4" s="6">
         <v>2</v>
@@ -6464,10 +7205,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
@@ -6481,10 +7222,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -6498,10 +7239,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -6515,10 +7256,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C8" s="6">
         <v>2</v>
@@ -6532,10 +7273,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -6549,10 +7290,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C10" s="6">
         <v>3</v>
@@ -6566,10 +7307,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -6583,10 +7324,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -6600,10 +7341,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C13" s="6">
         <v>2</v>
@@ -6617,10 +7358,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C14" s="6">
         <v>4</v>
@@ -6634,10 +7375,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -6651,10 +7392,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
@@ -6668,10 +7409,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="C17" s="6">
         <v>2</v>
@@ -6685,10 +7426,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
@@ -6702,10 +7443,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C19" s="6">
         <v>1</v>
@@ -6719,10 +7460,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C20" s="6">
         <v>2</v>
@@ -6736,10 +7477,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C21" s="6">
         <v>2</v>
@@ -6753,10 +7494,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
@@ -6770,10 +7511,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
@@ -6787,10 +7528,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C24" s="6">
         <v>1</v>
@@ -6799,6 +7540,788 @@
         <v>135000</v>
       </c>
       <c r="E24" s="6">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="6">
+        <v>2</v>
+      </c>
+      <c r="D25" s="6">
+        <v>125000</v>
+      </c>
+      <c r="E25" s="6">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6">
+        <v>95000</v>
+      </c>
+      <c r="E26" s="6">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2</v>
+      </c>
+      <c r="D27" s="6">
+        <v>120000</v>
+      </c>
+      <c r="E27" s="6">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" s="6">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6">
+        <v>90000</v>
+      </c>
+      <c r="E28" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1</v>
+      </c>
+      <c r="D29" s="6">
+        <v>180000</v>
+      </c>
+      <c r="E29" s="6">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6">
+        <v>75000</v>
+      </c>
+      <c r="E30" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C31" s="6">
+        <v>2</v>
+      </c>
+      <c r="D31" s="6">
+        <v>130000</v>
+      </c>
+      <c r="E31" s="6">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6">
+        <v>135000</v>
+      </c>
+      <c r="E32" s="6">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C33" s="6">
+        <v>3</v>
+      </c>
+      <c r="D33" s="6">
+        <v>140000</v>
+      </c>
+      <c r="E33" s="6">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
+      <c r="D34" s="6">
+        <v>80000</v>
+      </c>
+      <c r="E34" s="6">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1</v>
+      </c>
+      <c r="D35" s="6">
+        <v>150000</v>
+      </c>
+      <c r="E35" s="6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2</v>
+      </c>
+      <c r="D36" s="6">
+        <v>95000</v>
+      </c>
+      <c r="E36" s="6">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4</v>
+      </c>
+      <c r="D37" s="6">
+        <v>220000</v>
+      </c>
+      <c r="E37" s="6">
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1</v>
+      </c>
+      <c r="D38" s="6">
+        <v>65000</v>
+      </c>
+      <c r="E38" s="6">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" s="6">
+        <v>1</v>
+      </c>
+      <c r="D39" s="6">
+        <v>150000</v>
+      </c>
+      <c r="E39" s="6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="C40" s="6">
+        <v>2</v>
+      </c>
+      <c r="D40" s="6">
+        <v>840000</v>
+      </c>
+      <c r="E40" s="6">
+        <v>1680000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1</v>
+      </c>
+      <c r="D41" s="6">
+        <v>125000</v>
+      </c>
+      <c r="E41" s="6">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1</v>
+      </c>
+      <c r="D42" s="6">
+        <v>190000</v>
+      </c>
+      <c r="E42" s="6">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C43" s="6">
+        <v>2</v>
+      </c>
+      <c r="D43" s="6">
+        <v>300000</v>
+      </c>
+      <c r="E43" s="6">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" s="6">
+        <v>2</v>
+      </c>
+      <c r="D44" s="6">
+        <v>130000</v>
+      </c>
+      <c r="E44" s="6">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1</v>
+      </c>
+      <c r="D45" s="6">
+        <v>90000</v>
+      </c>
+      <c r="E45" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C46" s="6">
+        <v>1</v>
+      </c>
+      <c r="D46" s="23">
+        <v>240000</v>
+      </c>
+      <c r="E46" s="6">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1</v>
+      </c>
+      <c r="D47" s="6">
+        <v>135000</v>
+      </c>
+      <c r="E47" s="6">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="6">
+        <v>2</v>
+      </c>
+      <c r="D48" s="6">
+        <v>125000</v>
+      </c>
+      <c r="E48" s="6">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C49" s="6">
+        <v>1</v>
+      </c>
+      <c r="D49" s="6">
+        <v>95000</v>
+      </c>
+      <c r="E49" s="6">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" s="6">
+        <v>2</v>
+      </c>
+      <c r="D50" s="6">
+        <v>120000</v>
+      </c>
+      <c r="E50" s="6">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" s="6">
+        <v>1</v>
+      </c>
+      <c r="D51" s="6">
+        <v>90000</v>
+      </c>
+      <c r="E51" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C52" s="6">
+        <v>1</v>
+      </c>
+      <c r="D52" s="6">
+        <v>180000</v>
+      </c>
+      <c r="E52" s="6">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1</v>
+      </c>
+      <c r="D53" s="6">
+        <v>75000</v>
+      </c>
+      <c r="E53" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C54" s="6">
+        <v>2</v>
+      </c>
+      <c r="D54" s="6">
+        <v>130000</v>
+      </c>
+      <c r="E54" s="6">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1</v>
+      </c>
+      <c r="D55" s="6">
+        <v>135000</v>
+      </c>
+      <c r="E55" s="6">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C56" s="6">
+        <v>3</v>
+      </c>
+      <c r="D56" s="6">
+        <v>140000</v>
+      </c>
+      <c r="E56" s="6">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" s="6">
+        <v>1</v>
+      </c>
+      <c r="D57" s="6">
+        <v>80000</v>
+      </c>
+      <c r="E57" s="6">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" s="6">
+        <v>1</v>
+      </c>
+      <c r="D58" s="6">
+        <v>150000</v>
+      </c>
+      <c r="E58" s="6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C59" s="6">
+        <v>2</v>
+      </c>
+      <c r="D59" s="6">
+        <v>95000</v>
+      </c>
+      <c r="E59" s="6">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C60" s="6">
+        <v>4</v>
+      </c>
+      <c r="D60" s="6">
+        <v>220000</v>
+      </c>
+      <c r="E60" s="6">
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1</v>
+      </c>
+      <c r="D61" s="6">
+        <v>65000</v>
+      </c>
+      <c r="E61" s="6">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C62" s="6">
+        <v>1</v>
+      </c>
+      <c r="D62" s="6">
+        <v>150000</v>
+      </c>
+      <c r="E62" s="6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="C63" s="6">
+        <v>2</v>
+      </c>
+      <c r="D63" s="6">
+        <v>840000</v>
+      </c>
+      <c r="E63" s="6">
+        <v>1680000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C64" s="6">
+        <v>1</v>
+      </c>
+      <c r="D64" s="6">
+        <v>125000</v>
+      </c>
+      <c r="E64" s="6">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C65" s="6">
+        <v>1</v>
+      </c>
+      <c r="D65" s="6">
+        <v>190000</v>
+      </c>
+      <c r="E65" s="6">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C66" s="6">
+        <v>2</v>
+      </c>
+      <c r="D66" s="6">
+        <v>300000</v>
+      </c>
+      <c r="E66" s="6">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C67" s="6">
+        <v>2</v>
+      </c>
+      <c r="D67" s="6">
+        <v>130000</v>
+      </c>
+      <c r="E67" s="6">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C68" s="6">
+        <v>1</v>
+      </c>
+      <c r="D68" s="6">
+        <v>90000</v>
+      </c>
+      <c r="E68" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C69" s="6">
+        <v>1</v>
+      </c>
+      <c r="D69" s="23">
+        <v>240000</v>
+      </c>
+      <c r="E69" s="6">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C70" s="6">
+        <v>1</v>
+      </c>
+      <c r="D70" s="6">
+        <v>135000</v>
+      </c>
+      <c r="E70" s="6">
         <v>135000</v>
       </c>
     </row>
@@ -6830,10 +8353,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
@@ -6841,10 +8364,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -6852,10 +8375,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
@@ -6863,10 +8386,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
@@ -6874,10 +8397,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -6885,10 +8408,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -6896,10 +8419,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
@@ -6907,10 +8430,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -6918,10 +8441,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
@@ -6929,10 +8452,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -6940,10 +8463,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -6951,10 +8474,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -6962,10 +8485,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C14" s="6">
         <v>1</v>
@@ -6973,10 +8496,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -6984,10 +8507,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
@@ -6995,10 +8518,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C17" s="6">
         <v>1</v>
@@ -7006,10 +8529,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
@@ -7017,10 +8540,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C19" s="6">
         <v>2</v>
@@ -7028,10 +8551,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
@@ -7039,10 +8562,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C21" s="6">
         <v>1</v>
@@ -7050,10 +8573,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
@@ -7061,10 +8584,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
@@ -7072,10 +8595,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C24" s="6">
         <v>1</v>
@@ -7083,10 +8606,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C25" s="6">
         <v>2</v>
@@ -7094,10 +8617,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C26" s="6">
         <v>1</v>
@@ -7105,10 +8628,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C27" s="6">
         <v>1</v>
@@ -7116,10 +8639,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C28" s="6">
         <v>1</v>
@@ -7127,10 +8650,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C29" s="6">
         <v>1</v>
@@ -7138,10 +8661,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C30" s="6">
         <v>1</v>
@@ -7149,10 +8672,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C31" s="6">
         <v>2</v>
@@ -7160,10 +8683,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C32" s="6">
         <v>2</v>
@@ -7171,10 +8694,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C33" s="6">
         <v>2</v>
@@ -7182,10 +8705,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C34" s="6">
         <v>1</v>
@@ -7193,10 +8716,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C35" s="6">
         <v>2</v>
@@ -7204,10 +8727,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C36" s="6">
         <v>1</v>
@@ -7215,10 +8738,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="C37" s="6">
         <v>1</v>
@@ -7226,10 +8749,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C38" s="6">
         <v>2</v>
@@ -7237,10 +8760,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C39" s="6">
         <v>1</v>
@@ -7248,10 +8771,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C40" s="6">
         <v>2</v>
@@ -7259,10 +8782,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C41" s="6">
         <v>2</v>
@@ -7270,10 +8793,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C42" s="6">
         <v>2</v>
@@ -7281,10 +8804,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C43" s="6">
         <v>1</v>
@@ -7292,10 +8815,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C44" s="6">
         <v>1</v>
@@ -7303,10 +8826,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="C45" s="6">
         <v>1</v>
@@ -7314,10 +8837,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C46" s="6">
         <v>2</v>
@@ -7325,10 +8848,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C47" s="6">
         <v>1</v>
@@ -7336,10 +8859,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C48" s="6">
         <v>2</v>
@@ -7347,10 +8870,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C49" s="6">
         <v>2</v>
@@ -7358,10 +8881,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -7369,10 +8892,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C51" s="6">
         <v>1</v>
@@ -7380,10 +8903,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C52" s="6">
         <v>2</v>
@@ -7391,10 +8914,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C53" s="6">
         <v>1</v>
@@ -7402,10 +8925,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C54" s="6">
         <v>2</v>

--- a/QuanLyNhaHang.xlsx
+++ b/QuanLyNhaHang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐỒ ÁN IT008\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B78C21-8F41-4BC3-B83C-F8256B7C54E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCE9A63-F73C-4A7B-82A5-FA0107CD4B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="KhachHang" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,9 @@
     <sheet name="Category" sheetId="6" r:id="rId3"/>
     <sheet name="MonAn" sheetId="5" r:id="rId4"/>
     <sheet name="HoaDon" sheetId="2" r:id="rId5"/>
-    <sheet name="CTHD" sheetId="4" r:id="rId6"/>
-    <sheet name="ComboCT" sheetId="7" r:id="rId7"/>
+    <sheet name="Voucher" sheetId="8" r:id="rId6"/>
+    <sheet name="CTHD" sheetId="4" r:id="rId7"/>
+    <sheet name="ComboCT" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="758">
   <si>
     <t>MaKH</t>
   </si>
@@ -60,9 +61,6 @@
     <t>ThanhTien</t>
   </si>
   <si>
-    <t>GhiChu</t>
-  </si>
-  <si>
     <t>MaMon</t>
   </si>
   <si>
@@ -186,22 +184,34 @@
     <t>B10</t>
   </si>
   <si>
-    <t>Chưa thanh toán</t>
-  </si>
-  <si>
-    <t>Trả một phần</t>
-  </si>
-  <si>
-    <t>Chờ xác nhận</t>
+    <t>2023-07-01</t>
+  </si>
+  <si>
+    <t>2023-07-15</t>
   </si>
   <si>
     <t>Đã thanh toán</t>
   </si>
   <si>
-    <t>Khách đặt bàn trước</t>
-  </si>
-  <si>
-    <t>Giảm giá 10%</t>
+    <t>2023-07-22</t>
+  </si>
+  <si>
+    <t>2023-07-29</t>
+  </si>
+  <si>
+    <t>2023-08-05</t>
+  </si>
+  <si>
+    <t>2023-08-12</t>
+  </si>
+  <si>
+    <t>2023-08-19</t>
+  </si>
+  <si>
+    <t>2023-08-26</t>
+  </si>
+  <si>
+    <t>2023-09-02</t>
   </si>
   <si>
     <t>L01</t>
@@ -228,12 +238,6 @@
     <t>Món Chính</t>
   </si>
   <si>
-    <t>L05</t>
-  </si>
-  <si>
-    <t>Lẩu</t>
-  </si>
-  <si>
     <t>L06</t>
   </si>
   <si>
@@ -501,9 +505,6 @@
     <t>Nhiều rau củ, đẹp mắt</t>
   </si>
   <si>
-    <t>Còn</t>
-  </si>
-  <si>
     <t>Súp ngô kem</t>
   </si>
   <si>
@@ -1941,75 +1942,380 @@
     <t>combo_nhom_nho_1</t>
   </si>
   <si>
-    <t>HD011</t>
-  </si>
-  <si>
-    <t>HD012</t>
-  </si>
-  <si>
-    <t>HD013</t>
-  </si>
-  <si>
-    <t>HD014</t>
-  </si>
-  <si>
-    <t>HD015</t>
-  </si>
-  <si>
-    <t>HD016</t>
-  </si>
-  <si>
-    <t>HD017</t>
-  </si>
-  <si>
-    <t>HD018</t>
-  </si>
-  <si>
-    <t>HD019</t>
-  </si>
-  <si>
-    <t>HD020</t>
-  </si>
-  <si>
-    <t>HD021</t>
-  </si>
-  <si>
-    <t>HD022</t>
-  </si>
-  <si>
-    <t>HD023</t>
-  </si>
-  <si>
-    <t>HD024</t>
-  </si>
-  <si>
-    <t>HD025</t>
-  </si>
-  <si>
-    <t>HD026</t>
-  </si>
-  <si>
-    <t>HD027</t>
-  </si>
-  <si>
-    <t>HD028</t>
-  </si>
-  <si>
-    <t>HD029</t>
-  </si>
-  <si>
-    <t>HD030</t>
+    <t>TagTinhChat</t>
+  </si>
+  <si>
+    <t>TagMucDich</t>
+  </si>
+  <si>
+    <t>Nóng, Thơm, Dịu</t>
+  </si>
+  <si>
+    <t>Nóng, Mặn, Dịu</t>
+  </si>
+  <si>
+    <t>Nóng, Ngọt, Thanh</t>
+  </si>
+  <si>
+    <t>Nóng, Béo, Ngọt</t>
+  </si>
+  <si>
+    <t>Nóng, Thơm, Mặn</t>
+  </si>
+  <si>
+    <t>Lạnh, Chua, Ngọt</t>
+  </si>
+  <si>
+    <t>Nóng, Giòn, Mặn</t>
+  </si>
+  <si>
+    <t>Nóng, Giòn, Mặn, Béo</t>
+  </si>
+  <si>
+    <t>Nóng, Mặn, Cay, Ngọt</t>
+  </si>
+  <si>
+    <t>Nóng, Mặn, Thơm</t>
+  </si>
+  <si>
+    <t>Lạnh, Mặn, Thơm</t>
+  </si>
+  <si>
+    <t>Nóng, Mặn, Thơm, Béo</t>
+  </si>
+  <si>
+    <t>Nóng, Cay, Mặn, Thơm</t>
+  </si>
+  <si>
+    <t>Nóng, Mặn, Chua, Thơm</t>
+  </si>
+  <si>
+    <t>Nóng, Giòn, Chua, Mặn</t>
+  </si>
+  <si>
+    <t>Nóng, Dịu, Ngọt</t>
+  </si>
+  <si>
+    <t>Nóng, Thơm, Mặn, Thanh</t>
+  </si>
+  <si>
+    <t>Giữ ấm, Khai vị</t>
+  </si>
+  <si>
+    <t>Giải nhiệt, Ăn kèm</t>
+  </si>
+  <si>
+    <t>Giải nhiệt, Món chính</t>
+  </si>
+  <si>
+    <t>Ăn kèm, Ăn vặt</t>
+  </si>
+  <si>
+    <t>Giải nhiệt, Khai vị</t>
+  </si>
+  <si>
+    <t>Món chính, Ăn kèm</t>
+  </si>
+  <si>
+    <t>Món chính</t>
+  </si>
+  <si>
+    <t>Món chính, Khai vị</t>
+  </si>
+  <si>
+    <t>Món chính, Nhanh</t>
+  </si>
+  <si>
+    <t>Món chính, Đặc biệt</t>
+  </si>
+  <si>
+    <t>Món chính, Bổ dưỡng</t>
+  </si>
+  <si>
+    <t>Món chính, Đặc biệt, Hải sản</t>
+  </si>
+  <si>
+    <t>Nóng, Cay, Thơm, Béo</t>
+  </si>
+  <si>
+    <t>Món chính, Giữ ấm, Ăn chay</t>
+  </si>
+  <si>
+    <t>Nóng, Cay, Mặn</t>
+  </si>
+  <si>
+    <t>Món chính, Giữ ấm</t>
+  </si>
+  <si>
+    <t>Nóng, Chua, Thanh mát</t>
+  </si>
+  <si>
+    <t>Nóng, Dịu, Thơm</t>
+  </si>
+  <si>
+    <t>Món chính, Giữ ấm, Bổ dưỡng</t>
+  </si>
+  <si>
+    <t>Nóng, Cay, Chua, Mặn</t>
+  </si>
+  <si>
+    <t>Món chính, Giữ ấm, Hải sản</t>
+  </si>
+  <si>
+    <t>Nóng, Chua, Mặn, Dịu</t>
+  </si>
+  <si>
+    <t>Nóng, Cay, Chua, Thơm</t>
+  </si>
+  <si>
+    <t>Nóng, Cay, Chua</t>
+  </si>
+  <si>
+    <t>Nóng, Dịu, Thanh</t>
+  </si>
+  <si>
+    <t>Nóng, Mặn, Thơm, Dịu</t>
+  </si>
+  <si>
+    <t>Nóng, Dịu, Thơm, Ngọt</t>
+  </si>
+  <si>
+    <t>Nóng, Béo, Thơm, Dịu, Ngọt nhẹ</t>
+  </si>
+  <si>
+    <t>Món chính, Đặc biệt, Giữ ấm</t>
+  </si>
+  <si>
+    <t>Tráng miệng, Giải nhiệt</t>
+  </si>
+  <si>
+    <t>Nóng, Ngọt, Dịu</t>
+  </si>
+  <si>
+    <t>Tráng miệng, Giữ ấm, Bổ dưỡng</t>
+  </si>
+  <si>
+    <t>Lạnh, Ngọt, Béo</t>
+  </si>
+  <si>
+    <t>Lạnh, Ngọt, Béo, Thanh</t>
+  </si>
+  <si>
+    <t>Tráng miệng, Giải nhiệt, Đặc biệt</t>
+  </si>
+  <si>
+    <t>Lạnh, Ngọt, Dẻo</t>
+  </si>
+  <si>
+    <t>Lạnh, Ngọt, Béo, Thơm</t>
+  </si>
+  <si>
+    <t>Giải khát, Ăn kèm</t>
+  </si>
+  <si>
+    <t>Lạnh, Ngọt, Chua, Thanh</t>
+  </si>
+  <si>
+    <t>Lạnh, Ngọt, Thơm</t>
+  </si>
+  <si>
+    <t>Lạnh, Thanh</t>
+  </si>
+  <si>
+    <t>Giải khát, Ăn kèm, Đặc biệt</t>
+  </si>
+  <si>
+    <t>Ăn kèm, Rau xanh</t>
+  </si>
+  <si>
+    <t>Ăn kèm, Phụ trợ</t>
+  </si>
+  <si>
+    <t>Nóng, Giòn, Béo</t>
+  </si>
+  <si>
+    <t>Nóng, Béo, Thơm</t>
+  </si>
+  <si>
+    <t>Ăn kèm, Rau xanh, Bổ dưỡng</t>
+  </si>
+  <si>
+    <t>Nóng, Thơm, Béo, Mặn</t>
+  </si>
+  <si>
+    <t>Nước chấm, Ăn kèm</t>
+  </si>
+  <si>
+    <t>Nước chấm, Ăn kèm, Đặc biệt</t>
+  </si>
+  <si>
+    <t>Lạnh, Chua, Cay, Mặn</t>
+  </si>
+  <si>
+    <t>Lạnh, Chua, Ngọt, Thanh</t>
+  </si>
+  <si>
+    <t>Lạnh, Mặn, Chua</t>
+  </si>
+  <si>
+    <t>Ăn kèm, Giải ngán</t>
+  </si>
+  <si>
+    <t>Nóng, Cay, Thanh</t>
+  </si>
+  <si>
+    <t>Phụ trợ, Ăn kèm</t>
+  </si>
+  <si>
+    <t>Nóng, Mặn, Ngọt</t>
+  </si>
+  <si>
+    <t>Lạnh, Chua, Thanh</t>
+  </si>
+  <si>
+    <t>Lạnh, Chua, Cay, Ngọt</t>
+  </si>
+  <si>
+    <t>Lạnh, Thanh, Mặn</t>
+  </si>
+  <si>
+    <t>Lạnh, Thanh, Dịu</t>
+  </si>
+  <si>
+    <t>Lạnh, Thanh, Thơm</t>
+  </si>
+  <si>
+    <t>Nóng, Mặn, Béo, Thơm, Giòn</t>
+  </si>
+  <si>
+    <t>Nóng, Mặn, Thơm, Béo, Chua</t>
+  </si>
+  <si>
+    <t>Nóng, Ngọt, Mặn, Thơm</t>
+  </si>
+  <si>
+    <t>Nóng, Béo, Mặn</t>
+  </si>
+  <si>
+    <t>Nóng, Chua, Ngọt, Béo</t>
+  </si>
+  <si>
+    <t>Nóng, Thơm, Mặn, Chua, Béo</t>
+  </si>
+  <si>
+    <t>Nóng, Cay, Thơm, Thanh, Mặn</t>
+  </si>
+  <si>
+    <t>Lạnh, Ngọt, Thanh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lạnh, Ngọt, Thanh </t>
+  </si>
+  <si>
+    <t>Lạnh, Ngọt</t>
+  </si>
+  <si>
+    <t>Lạnh, Ngọt, Chua</t>
+  </si>
+  <si>
+    <t>Lạnh, Đắng</t>
+  </si>
+  <si>
+    <t>Lạnh, Thơm</t>
+  </si>
+  <si>
+    <t>Cay, Mặn</t>
+  </si>
+  <si>
+    <t>Lạnh, Béo</t>
+  </si>
+  <si>
+    <t>Béo, Mặn, Thơm</t>
+  </si>
+  <si>
+    <t>Ngọt, Chua, Cay</t>
+  </si>
+  <si>
+    <t>Chua, Cay, Ngọt</t>
+  </si>
+  <si>
+    <t>Cay, Thơm, Mặn</t>
+  </si>
+  <si>
+    <t>Lạnh, Mặn, Giòn</t>
+  </si>
+  <si>
+    <t>Giòn, Mặn</t>
+  </si>
+  <si>
+    <t>Béo, Mặn</t>
+  </si>
+  <si>
+    <t>Ăn kèm, Món chính</t>
+  </si>
+  <si>
+    <t>Ăn kèm, Khai vị</t>
+  </si>
+  <si>
+    <t>Món chính, Giữ ấm, Đặc biệt</t>
+  </si>
+  <si>
+    <t>Tráng miệng, Đặc biệt</t>
+  </si>
+  <si>
+    <t>Tráng miệng</t>
+  </si>
+  <si>
+    <t>Ăn kèm, Đặc biệt</t>
+  </si>
+  <si>
+    <t>Phụ trợ</t>
+  </si>
+  <si>
+    <t>Ăn kèm, Bổ dưỡng</t>
+  </si>
+  <si>
+    <t>Ăn kèm, Phụ trợ, Đặc biệt</t>
+  </si>
+  <si>
+    <t>Giữ ấm, Món chính</t>
+  </si>
+  <si>
+    <t>TENVC</t>
+  </si>
+  <si>
+    <t>SODIEMCANDOI</t>
+  </si>
+  <si>
+    <t>SOTIENDUOCGIAM</t>
+  </si>
+  <si>
+    <t>GIATRIHOADONTOITHIEU</t>
+  </si>
+  <si>
+    <t>Voucher Chào Bạn Mới</t>
+  </si>
+  <si>
+    <t>Giảm giá 50k</t>
+  </si>
+  <si>
+    <t>Giảm giá 100k</t>
+  </si>
+  <si>
+    <t>Voucher Tráng Miệng</t>
+  </si>
+  <si>
+    <t>Đại Tiệc VIP (Giảm 500k)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1000000]h:mm:ss;@"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2072,6 +2378,12 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2081,7 +2393,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -2128,13 +2440,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2194,9 +2545,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2209,13 +2557,31 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2552,110 +2918,110 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="C2" s="4">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="C3" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="C4" s="4">
         <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="C5" s="4">
         <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="C6" s="4">
         <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="C7" s="4">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
+      <c r="B9" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="C9" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
+      <c r="B11" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="C11" s="4">
         <v>20</v>
@@ -2687,112 +3053,112 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="6">
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="6">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="6">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="6">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="6">
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="6">
         <v>10</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="6">
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="6">
         <v>4</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="6">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="6">
         <v>12</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2802,7 +3168,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961555E7-CF7B-4FFF-91F2-23FDD704168F}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -2812,350 +3178,339 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C3" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>107</v>
+        <v>353</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>353</v>
+        <v>109</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3165,110 +3520,123 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{634218A2-E101-4BBA-A898-C4E343EFE595}">
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="39.109375" customWidth="1"/>
     <col min="3" max="3" width="34.44140625" customWidth="1"/>
     <col min="4" max="4" width="64.5546875" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="5" max="5" width="28.77734375" customWidth="1"/>
+    <col min="6" max="6" width="28.88671875" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="D2" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>638</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>655</v>
+      </c>
+      <c r="G2" s="6">
         <v>75000</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>159</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="D3" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>711</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>655</v>
+      </c>
+      <c r="G3" s="6">
         <v>125000</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>160</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="D4" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>640</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>655</v>
+      </c>
+      <c r="G4" s="6">
         <v>65000</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>161</v>
       </c>
@@ -3278,20 +3646,23 @@
       <c r="C5" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="D5" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>641</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>655</v>
+      </c>
+      <c r="G5" s="6">
         <v>80000</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>162</v>
       </c>
@@ -3301,296 +3672,335 @@
       <c r="C6" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="D6" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>642</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>655</v>
+      </c>
+      <c r="G6" s="6">
         <v>95000</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>163</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="D7" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>712</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>656</v>
+      </c>
+      <c r="G7" s="6">
         <v>90000</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>164</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>590</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="D8" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>714</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>656</v>
+      </c>
+      <c r="G8" s="6">
         <v>145000</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>165</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="D9" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>643</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>656</v>
+      </c>
+      <c r="G9" s="6">
         <v>120000</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>166</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="D10" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>714</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>656</v>
+      </c>
+      <c r="G10" s="6">
         <v>135000</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>167</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="D11" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>713</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>657</v>
+      </c>
+      <c r="G11" s="6">
         <v>100000</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>168</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="D12" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>644</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>658</v>
+      </c>
+      <c r="G12" s="6">
         <v>150000</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>169</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="D13" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>644</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>658</v>
+      </c>
+      <c r="G13" s="6">
         <v>100000</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>170</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F14" s="6">
+      <c r="D14" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>644</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>658</v>
+      </c>
+      <c r="G14" s="6">
         <v>130000</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>171</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F15" s="6">
+      <c r="D15" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>645</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>658</v>
+      </c>
+      <c r="G15" s="6">
         <v>90000</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>172</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F16" s="6">
+      <c r="D16" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>646</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>739</v>
+      </c>
+      <c r="G16" s="6">
         <v>120000</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>173</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F17" s="6">
+      <c r="D17" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>715</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>659</v>
+      </c>
+      <c r="G17" s="6">
         <v>95000</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F18" s="6">
+      <c r="D18" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>647</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>660</v>
+      </c>
+      <c r="G18" s="6">
         <v>110000</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>175</v>
       </c>
@@ -3600,66 +4010,75 @@
       <c r="C19" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F19" s="6">
+      <c r="D19" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>714</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>659</v>
+      </c>
+      <c r="G19" s="6">
         <v>95000</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>176</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F20" s="6">
+      <c r="D20" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>648</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>660</v>
+      </c>
+      <c r="G20" s="6">
         <v>100000</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>177</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="D21" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="F21" s="6">
+      <c r="E21" s="28" t="s">
+        <v>716</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>659</v>
+      </c>
+      <c r="G21" s="6">
         <v>85000</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>221</v>
       </c>
@@ -3669,20 +4088,23 @@
       <c r="C22" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="E22" s="28" t="s">
+        <v>717</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="G22" s="7">
         <v>135000</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>222</v>
       </c>
@@ -3692,20 +4114,23 @@
       <c r="C23" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="E23" s="28" t="s">
+        <v>718</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>664</v>
+      </c>
+      <c r="G23" s="7">
         <v>220000</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>223</v>
       </c>
@@ -3715,20 +4140,23 @@
       <c r="C24" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="E24" s="28" t="s">
+        <v>719</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>664</v>
+      </c>
+      <c r="G24" s="7">
         <v>120000</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>224</v>
       </c>
@@ -3738,20 +4166,23 @@
       <c r="C25" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E25" s="28" t="s">
+        <v>720</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>664</v>
+      </c>
+      <c r="G25" s="7">
         <v>140000</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>225</v>
       </c>
@@ -3761,20 +4192,23 @@
       <c r="C26" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="E26" s="28" t="s">
+        <v>721</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>664</v>
+      </c>
+      <c r="G26" s="7">
         <v>180000</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>226</v>
       </c>
@@ -3784,20 +4218,23 @@
       <c r="C27" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F27" s="7">
+      <c r="E27" s="28" t="s">
+        <v>722</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>665</v>
+      </c>
+      <c r="G27" s="7">
         <v>210000</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>227</v>
       </c>
@@ -3807,20 +4244,23 @@
       <c r="C28" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E28" s="28" t="s">
+        <v>650</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="G28" s="7">
         <v>190000</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>228</v>
       </c>
@@ -3830,20 +4270,23 @@
       <c r="C29" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="E29" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="G29" s="7">
         <v>175000</v>
       </c>
-      <c r="G29" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>229</v>
       </c>
@@ -3853,20 +4296,23 @@
       <c r="C30" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F30" s="7">
+      <c r="E30" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>662</v>
+      </c>
+      <c r="G30" s="7">
         <v>200000</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>230</v>
       </c>
@@ -3876,20 +4322,23 @@
       <c r="C31" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F31" s="7">
+      <c r="E31" s="28" t="s">
+        <v>723</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>740</v>
+      </c>
+      <c r="G31" s="7">
         <v>110000</v>
       </c>
-      <c r="G31" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>231</v>
       </c>
@@ -3899,20 +4348,23 @@
       <c r="C32" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F32" s="7">
+      <c r="E32" s="28" t="s">
+        <v>653</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>748</v>
+      </c>
+      <c r="G32" s="7">
         <v>95000</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>232</v>
       </c>
@@ -3922,20 +4374,23 @@
       <c r="C33" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="E33" s="28" t="s">
+        <v>654</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="G33" s="7">
         <v>85000</v>
       </c>
-      <c r="G33" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>233</v>
       </c>
@@ -3945,20 +4400,23 @@
       <c r="C34" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F34" s="7">
+      <c r="E34" s="28" t="s">
+        <v>647</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="G34" s="7">
         <v>90000</v>
       </c>
-      <c r="G34" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>234</v>
       </c>
@@ -3968,20 +4426,23 @@
       <c r="C35" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="E35" s="28" t="s">
+        <v>649</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="G35" s="7">
         <v>130000</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>235</v>
       </c>
@@ -3991,20 +4452,23 @@
       <c r="C36" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F36" s="7">
+      <c r="E36" s="28" t="s">
+        <v>667</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>670</v>
+      </c>
+      <c r="G36" s="7">
         <v>100000</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>266</v>
       </c>
@@ -4014,20 +4478,23 @@
       <c r="C37" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="27" t="s">
         <v>282</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F37" s="7">
+      <c r="E37" s="28" t="s">
+        <v>669</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>670</v>
+      </c>
+      <c r="G37" s="7">
         <v>250000</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>267</v>
       </c>
@@ -4037,20 +4504,23 @@
       <c r="C38" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F38" s="7">
+      <c r="E38" s="28" t="s">
+        <v>653</v>
+      </c>
+      <c r="F38" s="28" t="s">
+        <v>741</v>
+      </c>
+      <c r="G38" s="7">
         <v>270000</v>
       </c>
-      <c r="G38" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>268</v>
       </c>
@@ -4060,20 +4530,23 @@
       <c r="C39" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F39" s="7">
+      <c r="E39" s="28" t="s">
+        <v>671</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>670</v>
+      </c>
+      <c r="G39" s="7">
         <v>230000</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>269</v>
       </c>
@@ -4083,20 +4556,23 @@
       <c r="C40" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F40" s="7">
+      <c r="E40" s="28" t="s">
+        <v>672</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>673</v>
+      </c>
+      <c r="G40" s="7">
         <v>290000</v>
       </c>
-      <c r="G40" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>270</v>
       </c>
@@ -4106,20 +4582,23 @@
       <c r="C41" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F41" s="7">
+      <c r="E41" s="28" t="s">
+        <v>674</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>675</v>
+      </c>
+      <c r="G41" s="7">
         <v>280000</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>271</v>
       </c>
@@ -4129,20 +4608,23 @@
       <c r="C42" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="27" t="s">
         <v>287</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F42" s="7">
+      <c r="E42" s="28" t="s">
+        <v>676</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>675</v>
+      </c>
+      <c r="G42" s="7">
         <v>240000</v>
       </c>
-      <c r="G42" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>272</v>
       </c>
@@ -4152,20 +4634,23 @@
       <c r="C43" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="27" t="s">
         <v>288</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F43" s="7">
+      <c r="E43" s="28" t="s">
+        <v>649</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>675</v>
+      </c>
+      <c r="G43" s="7">
         <v>300000</v>
       </c>
-      <c r="G43" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>273</v>
       </c>
@@ -4175,20 +4660,23 @@
       <c r="C44" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F44" s="7">
+      <c r="E44" s="28" t="s">
+        <v>677</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>670</v>
+      </c>
+      <c r="G44" s="7">
         <v>190000</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>274</v>
       </c>
@@ -4198,20 +4686,23 @@
       <c r="C45" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F45" s="7">
+      <c r="E45" s="28" t="s">
+        <v>678</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>668</v>
+      </c>
+      <c r="G45" s="7">
         <v>195000</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>275</v>
       </c>
@@ -4221,20 +4712,23 @@
       <c r="C46" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F46" s="7">
+      <c r="E46" s="28" t="s">
+        <v>709</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>741</v>
+      </c>
+      <c r="G46" s="7">
         <v>350000</v>
       </c>
-      <c r="G46" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H46" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>276</v>
       </c>
@@ -4244,20 +4738,23 @@
       <c r="C47" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F47" s="7">
+      <c r="E47" s="28" t="s">
+        <v>680</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>741</v>
+      </c>
+      <c r="G47" s="7">
         <v>330000</v>
       </c>
-      <c r="G47" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H47" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>277</v>
       </c>
@@ -4270,17 +4767,20 @@
       <c r="D48" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F48" s="7">
+      <c r="E48" s="28" t="s">
+        <v>681</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>670</v>
+      </c>
+      <c r="G48" s="7">
         <v>379000</v>
       </c>
-      <c r="G48" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>278</v>
       </c>
@@ -4293,17 +4793,20 @@
       <c r="D49" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="E49" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="F49" s="16">
+      <c r="E49" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>683</v>
+      </c>
+      <c r="G49" s="16">
         <v>500000</v>
       </c>
-      <c r="G49" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H49" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>279</v>
       </c>
@@ -4313,20 +4816,23 @@
       <c r="C50" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="26" t="s">
         <v>354</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F50" s="17">
+      <c r="E50" s="28" t="s">
+        <v>724</v>
+      </c>
+      <c r="F50" s="28" t="s">
+        <v>684</v>
+      </c>
+      <c r="G50" s="17">
         <v>79000</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>280</v>
       </c>
@@ -4336,20 +4842,23 @@
       <c r="C51" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F51" s="17">
+      <c r="E51" s="28" t="s">
+        <v>725</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>684</v>
+      </c>
+      <c r="G51" s="17">
         <v>69000</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H51" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>281</v>
       </c>
@@ -4359,20 +4868,23 @@
       <c r="C52" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F52" s="17">
+      <c r="E52" s="28" t="s">
+        <v>724</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>684</v>
+      </c>
+      <c r="G52" s="17">
         <v>59000</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H52" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>340</v>
       </c>
@@ -4382,20 +4894,23 @@
       <c r="C53" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F53" s="17">
+      <c r="E53" s="28" t="s">
+        <v>712</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>684</v>
+      </c>
+      <c r="G53" s="17">
         <v>69000</v>
       </c>
-      <c r="G53" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H53" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>341</v>
       </c>
@@ -4405,20 +4920,23 @@
       <c r="C54" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D54" s="30" t="s">
         <v>329</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F54" s="14">
+      <c r="E54" s="28" t="s">
+        <v>688</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>684</v>
+      </c>
+      <c r="G54" s="14">
         <v>55000</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H54" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>342</v>
       </c>
@@ -4428,20 +4946,23 @@
       <c r="C55" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D55" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F55" s="17">
+      <c r="E55" s="28" t="s">
+        <v>685</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>686</v>
+      </c>
+      <c r="G55" s="17">
         <v>45000</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H55" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>343</v>
       </c>
@@ -4451,20 +4972,23 @@
       <c r="C56" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F56" s="17">
+      <c r="E56" s="28" t="s">
+        <v>691</v>
+      </c>
+      <c r="F56" s="28" t="s">
+        <v>684</v>
+      </c>
+      <c r="G56" s="17">
         <v>59000</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H56" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>344</v>
       </c>
@@ -4474,20 +4998,23 @@
       <c r="C57" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F57" s="17">
+      <c r="E57" s="28" t="s">
+        <v>640</v>
+      </c>
+      <c r="F57" s="28" t="s">
+        <v>686</v>
+      </c>
+      <c r="G57" s="17">
         <v>65000</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H57" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>345</v>
       </c>
@@ -4497,20 +5024,23 @@
       <c r="C58" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F58" s="17">
+      <c r="E58" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="F58" s="28" t="s">
+        <v>684</v>
+      </c>
+      <c r="G58" s="17">
         <v>79000</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H58" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>346</v>
       </c>
@@ -4520,20 +5050,23 @@
       <c r="C59" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F59" s="17">
+      <c r="E59" s="28" t="s">
+        <v>688</v>
+      </c>
+      <c r="F59" s="28" t="s">
+        <v>689</v>
+      </c>
+      <c r="G59" s="17">
         <v>69000</v>
       </c>
-      <c r="G59" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H59" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>347</v>
       </c>
@@ -4543,20 +5076,23 @@
       <c r="C60" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="D60" s="18" t="s">
+      <c r="D60" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F60" s="14">
+      <c r="E60" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="F60" s="28" t="s">
+        <v>689</v>
+      </c>
+      <c r="G60" s="14">
         <v>65000</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H60" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>348</v>
       </c>
@@ -4566,20 +5102,23 @@
       <c r="C61" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="D61" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F61" s="17">
+      <c r="E61" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="F61" s="28" t="s">
+        <v>684</v>
+      </c>
+      <c r="G61" s="17">
         <v>45000</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H61" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>349</v>
       </c>
@@ -4589,20 +5128,23 @@
       <c r="C62" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="D62" s="18" t="s">
+      <c r="D62" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F62" s="17">
+      <c r="E62" s="28" t="s">
+        <v>691</v>
+      </c>
+      <c r="F62" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="G62" s="17">
         <v>69000</v>
       </c>
-      <c r="G62" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H62" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>350</v>
       </c>
@@ -4612,20 +5154,23 @@
       <c r="C63" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="D63" s="30" t="s">
         <v>338</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F63" s="17">
+      <c r="E63" s="28" t="s">
+        <v>690</v>
+      </c>
+      <c r="F63" s="28" t="s">
+        <v>743</v>
+      </c>
+      <c r="G63" s="17">
         <v>55000</v>
       </c>
-      <c r="G63" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H63" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>351</v>
       </c>
@@ -4635,20 +5180,23 @@
       <c r="C64" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="D64" s="18" t="s">
+      <c r="D64" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F64" s="14">
+      <c r="E64" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="F64" s="28" t="s">
+        <v>743</v>
+      </c>
+      <c r="G64" s="14">
         <v>49000</v>
       </c>
-      <c r="G64" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H64" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>352</v>
       </c>
@@ -4658,20 +5206,23 @@
       <c r="C65" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="E65" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F65" s="6">
+      <c r="E65" s="28" t="s">
+        <v>712</v>
+      </c>
+      <c r="F65" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G65" s="6">
         <v>60000</v>
       </c>
-      <c r="G65" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H65" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>392</v>
       </c>
@@ -4681,20 +5232,23 @@
       <c r="C66" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F66" s="6">
+      <c r="E66" s="28" t="s">
+        <v>688</v>
+      </c>
+      <c r="F66" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G66" s="6">
         <v>65000</v>
       </c>
-      <c r="G66" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H66" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>393</v>
       </c>
@@ -4704,20 +5258,23 @@
       <c r="C67" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="26" t="s">
         <v>417</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F67" s="6">
+      <c r="E67" s="32" t="s">
+        <v>724</v>
+      </c>
+      <c r="F67" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="G67" s="6">
         <v>45000</v>
       </c>
-      <c r="G67" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H67" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>394</v>
       </c>
@@ -4727,20 +5284,23 @@
       <c r="C68" s="11" t="s">
         <v>440</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="26" t="s">
         <v>418</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F68" s="6">
+      <c r="E68" s="28" t="s">
+        <v>693</v>
+      </c>
+      <c r="F68" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G68" s="6">
         <v>55000</v>
       </c>
-      <c r="G68" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H68" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>395</v>
       </c>
@@ -4750,20 +5310,23 @@
       <c r="C69" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="26" t="s">
         <v>419</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F69" s="6">
+      <c r="E69" s="28" t="s">
+        <v>643</v>
+      </c>
+      <c r="F69" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G69" s="6">
         <v>40000</v>
       </c>
-      <c r="G69" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H69" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>396</v>
       </c>
@@ -4773,20 +5336,23 @@
       <c r="C70" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="26" t="s">
         <v>420</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F70" s="6">
+      <c r="E70" s="28" t="s">
+        <v>694</v>
+      </c>
+      <c r="F70" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G70" s="6">
         <v>45000</v>
       </c>
-      <c r="G70" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H70" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>397</v>
       </c>
@@ -4796,20 +5362,23 @@
       <c r="C71" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F71" s="6">
+      <c r="E71" s="28" t="s">
+        <v>643</v>
+      </c>
+      <c r="F71" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G71" s="6">
         <v>38000</v>
       </c>
-      <c r="G71" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H71" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>398</v>
       </c>
@@ -4819,20 +5388,23 @@
       <c r="C72" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="26" t="s">
         <v>422</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F72" s="6">
+      <c r="E72" s="28" t="s">
+        <v>695</v>
+      </c>
+      <c r="F72" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G72" s="6">
         <v>20000</v>
       </c>
-      <c r="G72" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H72" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>399</v>
       </c>
@@ -4842,20 +5414,23 @@
       <c r="C73" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D73" s="26" t="s">
         <v>423</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F73" s="6">
+      <c r="E73" s="28" t="s">
+        <v>726</v>
+      </c>
+      <c r="F73" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G73" s="6">
         <v>30000</v>
       </c>
-      <c r="G73" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H73" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>400</v>
       </c>
@@ -4865,20 +5440,23 @@
       <c r="C74" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="26" t="s">
         <v>424</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F74" s="6">
+      <c r="E74" s="28" t="s">
+        <v>726</v>
+      </c>
+      <c r="F74" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G74" s="6">
         <v>30000</v>
       </c>
-      <c r="G74" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H74" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>401</v>
       </c>
@@ -4888,20 +5466,23 @@
       <c r="C75" s="11" t="s">
         <v>447</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="26" t="s">
         <v>425</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F75" s="6">
+      <c r="E75" s="28" t="s">
+        <v>727</v>
+      </c>
+      <c r="F75" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G75" s="6">
         <v>30000</v>
       </c>
-      <c r="G75" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H75" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>402</v>
       </c>
@@ -4911,20 +5492,23 @@
       <c r="C76" s="11" t="s">
         <v>448</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="26" t="s">
         <v>426</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F76" s="6">
+      <c r="E76" s="28" t="s">
+        <v>727</v>
+      </c>
+      <c r="F76" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G76" s="6">
         <v>30000</v>
       </c>
-      <c r="G76" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H76" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>403</v>
       </c>
@@ -4934,20 +5518,23 @@
       <c r="C77" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="26" t="s">
         <v>427</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F77" s="6">
+      <c r="E77" s="28" t="s">
+        <v>693</v>
+      </c>
+      <c r="F77" s="28" t="s">
+        <v>696</v>
+      </c>
+      <c r="G77" s="6">
         <v>160000</v>
       </c>
-      <c r="G77" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H77" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>404</v>
       </c>
@@ -4957,20 +5544,23 @@
       <c r="C78" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="26" t="s">
         <v>428</v>
       </c>
-      <c r="E78" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F78" s="6">
+      <c r="E78" s="28" t="s">
+        <v>693</v>
+      </c>
+      <c r="F78" s="28" t="s">
+        <v>696</v>
+      </c>
+      <c r="G78" s="6">
         <v>180000</v>
       </c>
-      <c r="G78" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H78" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>405</v>
       </c>
@@ -4980,20 +5570,23 @@
       <c r="C79" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="E79" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F79" s="6">
+      <c r="E79" s="28" t="s">
+        <v>693</v>
+      </c>
+      <c r="F79" s="28" t="s">
+        <v>696</v>
+      </c>
+      <c r="G79" s="6">
         <v>170000</v>
       </c>
-      <c r="G79" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H79" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>406</v>
       </c>
@@ -5003,20 +5596,23 @@
       <c r="C80" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" s="26" t="s">
         <v>430</v>
       </c>
-      <c r="E80" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F80" s="6">
+      <c r="E80" s="28" t="s">
+        <v>693</v>
+      </c>
+      <c r="F80" s="28" t="s">
+        <v>696</v>
+      </c>
+      <c r="G80" s="6">
         <v>220000</v>
       </c>
-      <c r="G80" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H80" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>407</v>
       </c>
@@ -5026,20 +5622,23 @@
       <c r="C81" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="26" t="s">
         <v>431</v>
       </c>
-      <c r="E81" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F81" s="6">
+      <c r="E81" s="28" t="s">
+        <v>728</v>
+      </c>
+      <c r="F81" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G81" s="6">
         <v>100000</v>
       </c>
-      <c r="G81" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H81" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>408</v>
       </c>
@@ -5049,20 +5648,23 @@
       <c r="C82" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" s="26" t="s">
         <v>432</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F82" s="6">
+      <c r="E82" s="28" t="s">
+        <v>728</v>
+      </c>
+      <c r="F82" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G82" s="6">
         <v>90000</v>
       </c>
-      <c r="G82" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H82" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>409</v>
       </c>
@@ -5072,20 +5674,23 @@
       <c r="C83" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="26" t="s">
         <v>433</v>
       </c>
-      <c r="E83" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F83" s="6">
+      <c r="E83" s="28" t="s">
+        <v>728</v>
+      </c>
+      <c r="F83" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="G83" s="6">
         <v>85000</v>
       </c>
-      <c r="G83" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H83" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>410</v>
       </c>
@@ -5095,20 +5700,23 @@
       <c r="C84" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D84" s="26" t="s">
         <v>434</v>
       </c>
-      <c r="E84" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F84" s="6">
+      <c r="E84" s="28" t="s">
+        <v>729</v>
+      </c>
+      <c r="F84" s="28" t="s">
+        <v>744</v>
+      </c>
+      <c r="G84" s="6">
         <v>130000</v>
       </c>
-      <c r="G84" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H84" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>411</v>
       </c>
@@ -5118,20 +5726,23 @@
       <c r="C85" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D85" s="26" t="s">
         <v>435</v>
       </c>
-      <c r="E85" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F85" s="6">
+      <c r="E85" s="28" t="s">
+        <v>729</v>
+      </c>
+      <c r="F85" s="28" t="s">
+        <v>744</v>
+      </c>
+      <c r="G85" s="6">
         <v>125000</v>
       </c>
-      <c r="G85" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H85" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
         <v>412</v>
       </c>
@@ -5141,20 +5752,23 @@
       <c r="C86" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D86" s="26" t="s">
         <v>436</v>
       </c>
-      <c r="E86" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F86" s="6">
+      <c r="E86" s="28" t="s">
+        <v>729</v>
+      </c>
+      <c r="F86" s="28" t="s">
+        <v>744</v>
+      </c>
+      <c r="G86" s="6">
         <v>200000</v>
       </c>
-      <c r="G86" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H86" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>413</v>
       </c>
@@ -5164,20 +5778,23 @@
       <c r="C87" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D87" s="26" t="s">
         <v>466</v>
       </c>
-      <c r="E87" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F87" s="6">
+      <c r="E87" s="25" t="s">
+        <v>679</v>
+      </c>
+      <c r="F87" s="25" t="s">
+        <v>745</v>
+      </c>
+      <c r="G87" s="6">
         <v>30000</v>
       </c>
-      <c r="G87" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H87" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>414</v>
       </c>
@@ -5187,20 +5804,23 @@
       <c r="C88" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="26" t="s">
         <v>467</v>
       </c>
-      <c r="E88" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F88" s="18">
+      <c r="E88" s="28" t="s">
+        <v>642</v>
+      </c>
+      <c r="F88" s="28" t="s">
+        <v>698</v>
+      </c>
+      <c r="G88" s="18">
         <v>35000</v>
       </c>
-      <c r="G88" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H88" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>474</v>
       </c>
@@ -5210,20 +5830,23 @@
       <c r="C89" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D89" s="26" t="s">
         <v>468</v>
       </c>
-      <c r="E89" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F89" s="6">
+      <c r="E89" s="28" t="s">
+        <v>647</v>
+      </c>
+      <c r="F89" s="28" t="s">
+        <v>663</v>
+      </c>
+      <c r="G89" s="6">
         <v>70000</v>
       </c>
-      <c r="G89" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H89" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>475</v>
       </c>
@@ -5233,20 +5856,23 @@
       <c r="C90" s="11" t="s">
         <v>551</v>
       </c>
-      <c r="D90" s="18" t="s">
+      <c r="D90" s="30" t="s">
         <v>469</v>
       </c>
-      <c r="E90" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F90" s="6">
+      <c r="E90" s="28" t="s">
+        <v>695</v>
+      </c>
+      <c r="F90" s="28" t="s">
+        <v>745</v>
+      </c>
+      <c r="G90" s="6">
         <v>25000</v>
       </c>
-      <c r="G90" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H90" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
         <v>476</v>
       </c>
@@ -5256,20 +5882,23 @@
       <c r="C91" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="D91" s="26" t="s">
         <v>470</v>
       </c>
-      <c r="E91" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F91" s="6">
+      <c r="E91" s="25" t="s">
+        <v>702</v>
+      </c>
+      <c r="F91" s="25" t="s">
+        <v>663</v>
+      </c>
+      <c r="G91" s="6">
         <v>70000</v>
       </c>
-      <c r="G91" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H91" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>477</v>
       </c>
@@ -5279,20 +5908,23 @@
       <c r="C92" s="11" t="s">
         <v>557</v>
       </c>
-      <c r="D92" s="6" t="s">
+      <c r="D92" s="26" t="s">
         <v>471</v>
       </c>
-      <c r="E92" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F92" s="6">
+      <c r="E92" s="28" t="s">
+        <v>700</v>
+      </c>
+      <c r="F92" s="28" t="s">
+        <v>663</v>
+      </c>
+      <c r="G92" s="6">
         <v>85000</v>
       </c>
-      <c r="G92" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H92" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
         <v>478</v>
       </c>
@@ -5302,20 +5934,23 @@
       <c r="C93" s="11" t="s">
         <v>567</v>
       </c>
-      <c r="D93" s="18" t="s">
+      <c r="D93" s="30" t="s">
         <v>472</v>
       </c>
-      <c r="E93" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F93" s="18">
+      <c r="E93" s="28" t="s">
+        <v>699</v>
+      </c>
+      <c r="F93" s="28" t="s">
+        <v>658</v>
+      </c>
+      <c r="G93" s="18">
         <v>60000</v>
       </c>
-      <c r="G93" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H93" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
         <v>479</v>
       </c>
@@ -5325,20 +5960,23 @@
       <c r="C94" s="12" t="s">
         <v>554</v>
       </c>
-      <c r="D94" s="21" t="s">
+      <c r="D94" s="31" t="s">
         <v>473</v>
       </c>
-      <c r="E94" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F94" s="9">
+      <c r="E94" s="25" t="s">
+        <v>679</v>
+      </c>
+      <c r="F94" s="25" t="s">
+        <v>710</v>
+      </c>
+      <c r="G94" s="9">
         <v>45000</v>
       </c>
-      <c r="G94" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H94" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
         <v>480</v>
       </c>
@@ -5348,20 +5986,23 @@
       <c r="C95" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D95" s="26" t="s">
         <v>486</v>
       </c>
-      <c r="E95" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F95" s="6">
+      <c r="E95" s="28" t="s">
+        <v>642</v>
+      </c>
+      <c r="F95" s="28" t="s">
+        <v>697</v>
+      </c>
+      <c r="G95" s="6">
         <v>50000</v>
       </c>
-      <c r="G95" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H95" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>493</v>
       </c>
@@ -5371,20 +6012,23 @@
       <c r="C96" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="D96" s="18" t="s">
+      <c r="D96" s="30" t="s">
         <v>488</v>
       </c>
-      <c r="E96" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F96" s="6">
+      <c r="E96" s="28" t="s">
+        <v>647</v>
+      </c>
+      <c r="F96" s="28" t="s">
+        <v>746</v>
+      </c>
+      <c r="G96" s="6">
         <v>65000</v>
       </c>
-      <c r="G96" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H96" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>494</v>
       </c>
@@ -5394,20 +6038,23 @@
       <c r="C97" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="26" t="s">
         <v>490</v>
       </c>
-      <c r="E97" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F97" s="6">
+      <c r="E97" s="28" t="s">
+        <v>642</v>
+      </c>
+      <c r="F97" s="28" t="s">
+        <v>697</v>
+      </c>
+      <c r="G97" s="6">
         <v>50000</v>
       </c>
-      <c r="G97" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H97" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>495</v>
       </c>
@@ -5417,20 +6064,23 @@
       <c r="C98" s="11" t="s">
         <v>553</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="26" t="s">
         <v>491</v>
       </c>
-      <c r="E98" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F98" s="6">
+      <c r="E98" s="28" t="s">
+        <v>639</v>
+      </c>
+      <c r="F98" s="28" t="s">
+        <v>701</v>
+      </c>
+      <c r="G98" s="6">
         <v>55000</v>
       </c>
-      <c r="G98" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H98" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
         <v>496</v>
       </c>
@@ -5440,20 +6090,23 @@
       <c r="C99" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="26" t="s">
         <v>483</v>
       </c>
-      <c r="E99" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F99" s="6">
+      <c r="E99" s="28" t="s">
+        <v>702</v>
+      </c>
+      <c r="F99" s="28" t="s">
+        <v>701</v>
+      </c>
+      <c r="G99" s="6">
         <v>65000</v>
       </c>
-      <c r="G99" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H99" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>497</v>
       </c>
@@ -5463,20 +6116,23 @@
       <c r="C100" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D100" s="26" t="s">
         <v>492</v>
       </c>
-      <c r="E100" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F100" s="6">
+      <c r="E100" s="28" t="s">
+        <v>647</v>
+      </c>
+      <c r="F100" s="28" t="s">
+        <v>701</v>
+      </c>
+      <c r="G100" s="6">
         <v>85000</v>
       </c>
-      <c r="G100" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H100" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>498</v>
       </c>
@@ -5486,20 +6142,23 @@
       <c r="C101" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="26" t="s">
         <v>513</v>
       </c>
-      <c r="E101" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F101" s="17">
+      <c r="E101" s="28" t="s">
+        <v>730</v>
+      </c>
+      <c r="F101" s="28" t="s">
+        <v>703</v>
+      </c>
+      <c r="G101" s="17">
         <v>5000</v>
       </c>
-      <c r="G101" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H101" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>527</v>
       </c>
@@ -5509,20 +6168,23 @@
       <c r="C102" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="D102" s="18" t="s">
+      <c r="D102" s="30" t="s">
         <v>514</v>
       </c>
-      <c r="E102" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F102" s="17">
+      <c r="E102" s="28" t="s">
+        <v>731</v>
+      </c>
+      <c r="F102" s="28" t="s">
+        <v>703</v>
+      </c>
+      <c r="G102" s="17">
         <v>8000</v>
       </c>
-      <c r="G102" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H102" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
         <v>528</v>
       </c>
@@ -5532,20 +6194,23 @@
       <c r="C103" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="26" t="s">
         <v>515</v>
       </c>
-      <c r="E103" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F103" s="14">
+      <c r="E103" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="F103" s="28" t="s">
+        <v>704</v>
+      </c>
+      <c r="G103" s="14">
         <v>15000</v>
       </c>
-      <c r="G103" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H103" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>529</v>
       </c>
@@ -5555,20 +6220,23 @@
       <c r="C104" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="D104" s="26" t="s">
         <v>516</v>
       </c>
-      <c r="E104" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F104" s="14">
+      <c r="E104" s="28" t="s">
+        <v>733</v>
+      </c>
+      <c r="F104" s="28" t="s">
+        <v>703</v>
+      </c>
+      <c r="G104" s="14">
         <v>12000</v>
       </c>
-      <c r="G104" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H104" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>530</v>
       </c>
@@ -5578,20 +6246,23 @@
       <c r="C105" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="26" t="s">
         <v>517</v>
       </c>
-      <c r="E105" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F105" s="14">
+      <c r="E105" s="28" t="s">
+        <v>734</v>
+      </c>
+      <c r="F105" s="28" t="s">
+        <v>703</v>
+      </c>
+      <c r="G105" s="14">
         <v>10000</v>
       </c>
-      <c r="G105" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H105" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>531</v>
       </c>
@@ -5601,20 +6272,23 @@
       <c r="C106" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D106" s="26" t="s">
         <v>518</v>
       </c>
-      <c r="E106" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F106" s="14">
+      <c r="E106" s="28" t="s">
+        <v>735</v>
+      </c>
+      <c r="F106" s="28" t="s">
+        <v>703</v>
+      </c>
+      <c r="G106" s="14">
         <v>10000</v>
       </c>
-      <c r="G106" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H106" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
         <v>532</v>
       </c>
@@ -5624,20 +6298,23 @@
       <c r="C107" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="26" t="s">
         <v>519</v>
       </c>
-      <c r="E107" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F107" s="14">
+      <c r="E107" s="28" t="s">
+        <v>730</v>
+      </c>
+      <c r="F107" s="28" t="s">
+        <v>703</v>
+      </c>
+      <c r="G107" s="14">
         <v>8000</v>
       </c>
-      <c r="G107" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H107" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>533</v>
       </c>
@@ -5647,20 +6324,23 @@
       <c r="C108" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="D108" s="26" t="s">
         <v>520</v>
       </c>
-      <c r="E108" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F108" s="17">
+      <c r="E108" s="28" t="s">
+        <v>705</v>
+      </c>
+      <c r="F108" s="28" t="s">
+        <v>708</v>
+      </c>
+      <c r="G108" s="17">
         <v>12000</v>
       </c>
-      <c r="G108" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H108" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
         <v>534</v>
       </c>
@@ -5670,20 +6350,23 @@
       <c r="C109" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D109" s="26" t="s">
         <v>526</v>
       </c>
-      <c r="E109" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F109" s="17">
+      <c r="E109" s="28" t="s">
+        <v>706</v>
+      </c>
+      <c r="F109" s="28" t="s">
+        <v>708</v>
+      </c>
+      <c r="G109" s="17">
         <v>10000</v>
       </c>
-      <c r="G109" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H109" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>535</v>
       </c>
@@ -5693,20 +6376,23 @@
       <c r="C110" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="D110" s="6" t="s">
+      <c r="D110" s="26" t="s">
         <v>521</v>
       </c>
-      <c r="E110" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F110" s="17">
+      <c r="E110" s="28" t="s">
+        <v>707</v>
+      </c>
+      <c r="F110" s="28" t="s">
+        <v>708</v>
+      </c>
+      <c r="G110" s="17">
         <v>10000</v>
       </c>
-      <c r="G110" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H110" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
         <v>536</v>
       </c>
@@ -5716,20 +6402,23 @@
       <c r="C111" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="26" t="s">
         <v>522</v>
       </c>
-      <c r="E111" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F111" s="17">
+      <c r="E111" s="28" t="s">
+        <v>736</v>
+      </c>
+      <c r="F111" s="28" t="s">
+        <v>708</v>
+      </c>
+      <c r="G111" s="17">
         <v>8000</v>
       </c>
-      <c r="G111" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H111" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>537</v>
       </c>
@@ -5739,20 +6428,23 @@
       <c r="C112" s="11" t="s">
         <v>549</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D112" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="E112" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F112" s="17">
+      <c r="E112" s="28" t="s">
+        <v>737</v>
+      </c>
+      <c r="F112" s="28" t="s">
+        <v>698</v>
+      </c>
+      <c r="G112" s="17">
         <v>12000</v>
       </c>
-      <c r="G112" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H112" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
         <v>538</v>
       </c>
@@ -5762,20 +6454,23 @@
       <c r="C113" s="11" t="s">
         <v>556</v>
       </c>
-      <c r="D113" s="18" t="s">
+      <c r="D113" s="30" t="s">
         <v>511</v>
       </c>
-      <c r="E113" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F113" s="17">
+      <c r="E113" s="28" t="s">
+        <v>705</v>
+      </c>
+      <c r="F113" s="28" t="s">
+        <v>708</v>
+      </c>
+      <c r="G113" s="17">
         <v>12000</v>
       </c>
-      <c r="G113" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H113" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>539</v>
       </c>
@@ -5785,20 +6480,23 @@
       <c r="C114" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="D114" s="18" t="s">
+      <c r="D114" s="30" t="s">
         <v>525</v>
       </c>
-      <c r="E114" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F114" s="17">
+      <c r="E114" s="28" t="s">
+        <v>738</v>
+      </c>
+      <c r="F114" s="28" t="s">
+        <v>747</v>
+      </c>
+      <c r="G114" s="17">
         <v>15000</v>
       </c>
-      <c r="G114" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H114" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>579</v>
       </c>
@@ -5808,20 +6506,19 @@
       <c r="C115" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="D115" s="18" t="s">
+      <c r="D115" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="E115" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F115" s="6">
+      <c r="E115" s="28"/>
+      <c r="F115" s="28"/>
+      <c r="G115" s="6">
         <v>503000</v>
       </c>
-      <c r="G115" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H115" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>580</v>
       </c>
@@ -5831,20 +6528,19 @@
       <c r="C116" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="26" t="s">
         <v>577</v>
       </c>
-      <c r="E116" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F116" s="6">
+      <c r="E116" s="28"/>
+      <c r="F116" s="28"/>
+      <c r="G116" s="6">
         <v>503000</v>
       </c>
-      <c r="G116" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H116" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>581</v>
       </c>
@@ -5854,20 +6550,19 @@
       <c r="C117" s="6" t="s">
         <v>629</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="26" t="s">
         <v>577</v>
       </c>
-      <c r="E117" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F117" s="6">
+      <c r="E117" s="28"/>
+      <c r="F117" s="28"/>
+      <c r="G117" s="6">
         <v>665000</v>
       </c>
-      <c r="G117" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H117" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>582</v>
       </c>
@@ -5877,20 +6572,19 @@
       <c r="C118" s="6" t="s">
         <v>635</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="D118" s="26" t="s">
         <v>578</v>
       </c>
-      <c r="E118" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F118" s="6">
+      <c r="E118" s="28"/>
+      <c r="F118" s="28"/>
+      <c r="G118" s="6">
         <v>840000</v>
       </c>
-      <c r="G118" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H118" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>583</v>
       </c>
@@ -5900,20 +6594,19 @@
       <c r="C119" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="D119" s="26" t="s">
         <v>578</v>
       </c>
-      <c r="E119" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F119" s="6">
+      <c r="E119" s="28"/>
+      <c r="F119" s="28"/>
+      <c r="G119" s="6">
         <v>970000</v>
       </c>
-      <c r="G119" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H119" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>584</v>
       </c>
@@ -5923,20 +6616,19 @@
       <c r="C120" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="D120" s="6" t="s">
+      <c r="D120" s="26" t="s">
         <v>578</v>
       </c>
-      <c r="E120" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F120" s="6">
+      <c r="E120" s="28"/>
+      <c r="F120" s="28"/>
+      <c r="G120" s="6">
         <v>927000</v>
       </c>
-      <c r="G120" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H120" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
         <v>585</v>
       </c>
@@ -5946,20 +6638,19 @@
       <c r="C121" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="D121" s="6" t="s">
+      <c r="D121" s="26" t="s">
         <v>588</v>
       </c>
-      <c r="E121" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F121" s="6">
+      <c r="E121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="6">
         <v>1537000</v>
       </c>
-      <c r="G121" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H121" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>586</v>
       </c>
@@ -5969,20 +6660,19 @@
       <c r="C122" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="D122" s="6" t="s">
+      <c r="D122" s="26" t="s">
         <v>588</v>
       </c>
-      <c r="E122" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F122" s="6">
+      <c r="E122" s="28"/>
+      <c r="F122" s="28"/>
+      <c r="G122" s="6">
         <v>1470000</v>
       </c>
-      <c r="G122" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H122" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>587</v>
       </c>
@@ -5992,26 +6682,20 @@
       <c r="C123" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="D123" s="6" t="s">
+      <c r="D123" s="26" t="s">
         <v>588</v>
       </c>
-      <c r="E123" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F123" s="6">
+      <c r="E123" s="28"/>
+      <c r="F123" s="28"/>
+      <c r="G123" s="6">
         <v>1912000</v>
       </c>
-      <c r="G123" s="6" t="s">
-        <v>75</v>
+      <c r="H123" s="6" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E21 E24:E35 E39:E47 E50:E51 E55:E62 E73:E74 E65:E70 E78:E84 E87:E89 E91:E92 E96:E103 E113:E117 E106:E110 E120:E121 E123" xr:uid="{8E11C00A-01D6-4A29-9552-AE5E472EB2FD}">
-      <formula1>"Còn, Tạm Ngưng, Hết"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6019,22 +6703,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C67116-806E-4F8F-AE20-17E61EFDB4E5}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.88671875" customWidth="1"/>
     <col min="4" max="4" width="14.88671875" customWidth="1"/>
     <col min="5" max="5" width="19.109375" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" style="28" customWidth="1"/>
+    <col min="6" max="6" width="20.88671875" customWidth="1"/>
     <col min="7" max="7" width="16.21875" customWidth="1"/>
     <col min="8" max="8" width="14.44140625" customWidth="1"/>
     <col min="9" max="9" width="20.6640625" customWidth="1"/>
     <col min="10" max="10" width="20.44140625" customWidth="1"/>
-    <col min="11" max="11" width="18.77734375" customWidth="1"/>
-    <col min="12" max="12" width="18.88671875" customWidth="1"/>
+    <col min="11" max="11" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -6050,7 +6733,7 @@
       <c r="E1" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -6065,28 +6748,25 @@
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>614</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>593</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="21" t="s">
         <v>594</v>
       </c>
-      <c r="F2" s="27">
-        <v>45953</v>
+      <c r="F2" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="G2" s="7">
         <v>585000</v>
@@ -6098,30 +6778,27 @@
         <v>580745</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K2" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>615</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>595</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="21" t="s">
         <v>604</v>
       </c>
-      <c r="F3" s="27">
-        <v>45953</v>
+      <c r="F3" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="G3" s="7">
         <v>270000</v>
@@ -6133,30 +6810,27 @@
         <v>250000</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>616</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="21" t="s">
         <v>596</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="21" t="s">
         <v>605</v>
       </c>
-      <c r="F4" s="27">
-        <v>45953</v>
+      <c r="F4" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="G4" s="7">
         <v>890000</v>
@@ -6168,30 +6842,27 @@
         <v>890000</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>617</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>597</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="21" t="s">
         <v>606</v>
       </c>
-      <c r="F5" s="27">
-        <v>45954</v>
+      <c r="F5" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="G5" s="7">
         <v>230000</v>
@@ -6203,30 +6874,27 @@
         <v>230000</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>618</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>598</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="21" t="s">
         <v>607</v>
       </c>
-      <c r="F6" s="27">
-        <v>45954</v>
+      <c r="F6" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="G6" s="7">
         <v>1070000</v>
@@ -6238,30 +6906,27 @@
         <v>1060500</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>619</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>599</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="21" t="s">
         <v>608</v>
       </c>
-      <c r="F7" s="27">
-        <v>45954</v>
+      <c r="F7" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="G7" s="7">
         <v>215000</v>
@@ -6273,30 +6938,27 @@
         <v>215000</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>620</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>600</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="21" t="s">
         <v>609</v>
       </c>
-      <c r="F8" s="27">
-        <v>45954</v>
+      <c r="F8" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="G8" s="7">
         <v>1680000</v>
@@ -6308,30 +6970,27 @@
         <v>1680000</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>621</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>601</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="21" t="s">
         <v>610</v>
       </c>
-      <c r="F9" s="27">
-        <v>45954</v>
+      <c r="F9" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="G9" s="7">
         <v>915000</v>
@@ -6343,30 +7002,27 @@
         <v>912000</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>622</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>602</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="21" t="s">
         <v>611</v>
       </c>
-      <c r="F10" s="27">
-        <v>45955</v>
+      <c r="F10" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="G10" s="7">
         <v>260000</v>
@@ -6378,30 +7034,27 @@
         <v>248000</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>623</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>603</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="21" t="s">
         <v>612</v>
       </c>
-      <c r="F11" s="27">
-        <v>45955</v>
+      <c r="F11" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="G11" s="7">
         <v>465000</v>
@@ -6413,710 +7066,7 @@
         <v>456000</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>636</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>593</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>594</v>
-      </c>
-      <c r="F12" s="27">
-        <v>45962</v>
-      </c>
-      <c r="G12" s="7">
-        <v>585000</v>
-      </c>
-      <c r="H12" s="7">
-        <v>4255</v>
-      </c>
-      <c r="I12" s="7">
-        <v>580745</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K12" s="7" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>595</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="F13" s="27">
-        <v>45962</v>
-      </c>
-      <c r="G13" s="7">
-        <v>270000</v>
-      </c>
-      <c r="H13" s="7">
-        <v>15000</v>
-      </c>
-      <c r="I13" s="7">
-        <v>250000</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>596</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>605</v>
-      </c>
-      <c r="F14" s="27">
-        <v>45966</v>
-      </c>
-      <c r="G14" s="7">
-        <v>890000</v>
-      </c>
-      <c r="H14" s="7">
-        <v>0</v>
-      </c>
-      <c r="I14" s="7">
-        <v>890000</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>639</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>597</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>606</v>
-      </c>
-      <c r="F15" s="27">
-        <v>45966</v>
-      </c>
-      <c r="G15" s="7">
-        <v>230000</v>
-      </c>
-      <c r="H15" s="7">
-        <v>0</v>
-      </c>
-      <c r="I15" s="7">
-        <v>230000</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>640</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>598</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>607</v>
-      </c>
-      <c r="F16" s="27">
-        <v>45966</v>
-      </c>
-      <c r="G16" s="7">
-        <v>1070000</v>
-      </c>
-      <c r="H16" s="7">
-        <v>9500</v>
-      </c>
-      <c r="I16" s="7">
-        <v>1060500</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>599</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>608</v>
-      </c>
-      <c r="F17" s="27">
-        <v>45967</v>
-      </c>
-      <c r="G17" s="7">
-        <v>215000</v>
-      </c>
-      <c r="H17" s="7">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7">
-        <v>215000</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>600</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>609</v>
-      </c>
-      <c r="F18" s="27">
-        <v>45967</v>
-      </c>
-      <c r="G18" s="7">
-        <v>1680000</v>
-      </c>
-      <c r="H18" s="7">
-        <v>0</v>
-      </c>
-      <c r="I18" s="6">
-        <v>1680000</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>601</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>610</v>
-      </c>
-      <c r="F19" s="27">
-        <v>45971</v>
-      </c>
-      <c r="G19" s="7">
-        <v>915000</v>
-      </c>
-      <c r="H19" s="7">
-        <v>3000</v>
-      </c>
-      <c r="I19" s="7">
-        <v>912000</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>602</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>611</v>
-      </c>
-      <c r="F20" s="27">
-        <v>45971</v>
-      </c>
-      <c r="G20" s="7">
-        <v>260000</v>
-      </c>
-      <c r="H20" s="7">
-        <v>12000</v>
-      </c>
-      <c r="I20" s="7">
-        <v>248000</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>645</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>612</v>
-      </c>
-      <c r="F21" s="27">
-        <v>45971</v>
-      </c>
-      <c r="G21" s="7">
-        <v>465000</v>
-      </c>
-      <c r="H21" s="7">
-        <v>9000</v>
-      </c>
-      <c r="I21" s="7">
-        <v>456000</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>593</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>594</v>
-      </c>
-      <c r="F22" s="27">
-        <v>46002</v>
-      </c>
-      <c r="G22" s="7">
-        <v>585000</v>
-      </c>
-      <c r="H22" s="7">
-        <v>4255</v>
-      </c>
-      <c r="I22" s="7">
-        <v>580745</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>595</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="F23" s="27">
-        <v>46002</v>
-      </c>
-      <c r="G23" s="7">
-        <v>270000</v>
-      </c>
-      <c r="H23" s="7">
-        <v>15000</v>
-      </c>
-      <c r="I23" s="7">
-        <v>250000</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>648</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>596</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>605</v>
-      </c>
-      <c r="F24" s="27">
-        <v>46002</v>
-      </c>
-      <c r="G24" s="7">
-        <v>890000</v>
-      </c>
-      <c r="H24" s="7">
-        <v>0</v>
-      </c>
-      <c r="I24" s="7">
-        <v>890000</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>649</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>597</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>606</v>
-      </c>
-      <c r="F25" s="27">
-        <v>46002</v>
-      </c>
-      <c r="G25" s="7">
-        <v>230000</v>
-      </c>
-      <c r="H25" s="7">
-        <v>0</v>
-      </c>
-      <c r="I25" s="7">
-        <v>230000</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>598</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>607</v>
-      </c>
-      <c r="F26" s="27">
-        <v>46005</v>
-      </c>
-      <c r="G26" s="7">
-        <v>1070000</v>
-      </c>
-      <c r="H26" s="7">
-        <v>9500</v>
-      </c>
-      <c r="I26" s="7">
-        <v>1060500</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>599</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>608</v>
-      </c>
-      <c r="F27" s="27">
-        <v>46005</v>
-      </c>
-      <c r="G27" s="7">
-        <v>215000</v>
-      </c>
-      <c r="H27" s="7">
-        <v>0</v>
-      </c>
-      <c r="I27" s="7">
-        <v>215000</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>600</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>609</v>
-      </c>
-      <c r="F28" s="27">
-        <v>46005</v>
-      </c>
-      <c r="G28" s="7">
-        <v>1680000</v>
-      </c>
-      <c r="H28" s="7">
-        <v>0</v>
-      </c>
-      <c r="I28" s="6">
-        <v>1680000</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>601</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>610</v>
-      </c>
-      <c r="F29" s="27">
-        <v>46015</v>
-      </c>
-      <c r="G29" s="7">
-        <v>915000</v>
-      </c>
-      <c r="H29" s="7">
-        <v>3000</v>
-      </c>
-      <c r="I29" s="7">
-        <v>912000</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>654</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>602</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>611</v>
-      </c>
-      <c r="F30" s="27">
-        <v>46016</v>
-      </c>
-      <c r="G30" s="7">
-        <v>260000</v>
-      </c>
-      <c r="H30" s="7">
-        <v>12000</v>
-      </c>
-      <c r="I30" s="7">
-        <v>248000</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>612</v>
-      </c>
-      <c r="F31" s="27">
-        <v>46016</v>
-      </c>
-      <c r="G31" s="7">
-        <v>465000</v>
-      </c>
-      <c r="H31" s="7">
-        <v>9000</v>
-      </c>
-      <c r="I31" s="7">
-        <v>456000</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -7127,8 +7077,108 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB8045E-019B-4C48-95E4-277488D1F302}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.77734375" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="23.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
+        <v>753</v>
+      </c>
+      <c r="B2" s="33">
+        <v>50</v>
+      </c>
+      <c r="C2" s="33">
+        <v>20000</v>
+      </c>
+      <c r="D2" s="33">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="33" t="s">
+        <v>754</v>
+      </c>
+      <c r="B3" s="33">
+        <v>400</v>
+      </c>
+      <c r="C3" s="33">
+        <v>50000</v>
+      </c>
+      <c r="D3" s="33">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>755</v>
+      </c>
+      <c r="B4" s="33">
+        <v>750</v>
+      </c>
+      <c r="C4" s="33">
+        <v>100000</v>
+      </c>
+      <c r="D4" s="33">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
+        <v>756</v>
+      </c>
+      <c r="B5" s="33">
+        <v>150</v>
+      </c>
+      <c r="C5" s="33">
+        <v>30000</v>
+      </c>
+      <c r="D5" s="33">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="33" t="s">
+        <v>757</v>
+      </c>
+      <c r="B6" s="33">
+        <v>3000</v>
+      </c>
+      <c r="C6" s="33">
+        <v>500000</v>
+      </c>
+      <c r="D6" s="33">
+        <v>3000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FC086EC-74CB-4344-93F9-D1F3265B5BB1}">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="4" width="9.88671875" customWidth="1"/>
@@ -7140,10 +7190,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>613</v>
@@ -7242,7 +7292,7 @@
         <v>616</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -7519,7 +7569,7 @@
       <c r="C23" s="6">
         <v>1</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="22">
         <v>240000</v>
       </c>
       <c r="E23" s="6">
@@ -7540,788 +7590,6 @@
         <v>135000</v>
       </c>
       <c r="E24" s="6">
-        <v>135000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C25" s="6">
-        <v>2</v>
-      </c>
-      <c r="D25" s="6">
-        <v>125000</v>
-      </c>
-      <c r="E25" s="6">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C26" s="6">
-        <v>1</v>
-      </c>
-      <c r="D26" s="6">
-        <v>95000</v>
-      </c>
-      <c r="E26" s="6">
-        <v>95000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C27" s="6">
-        <v>2</v>
-      </c>
-      <c r="D27" s="6">
-        <v>120000</v>
-      </c>
-      <c r="E27" s="6">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
-        <v>637</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C28" s="6">
-        <v>1</v>
-      </c>
-      <c r="D28" s="6">
-        <v>90000</v>
-      </c>
-      <c r="E28" s="6">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>637</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C29" s="6">
-        <v>1</v>
-      </c>
-      <c r="D29" s="6">
-        <v>180000</v>
-      </c>
-      <c r="E29" s="6">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C30" s="6">
-        <v>1</v>
-      </c>
-      <c r="D30" s="6">
-        <v>75000</v>
-      </c>
-      <c r="E30" s="6">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C31" s="6">
-        <v>2</v>
-      </c>
-      <c r="D31" s="6">
-        <v>130000</v>
-      </c>
-      <c r="E31" s="6">
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C32" s="6">
-        <v>1</v>
-      </c>
-      <c r="D32" s="6">
-        <v>135000</v>
-      </c>
-      <c r="E32" s="6">
-        <v>135000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C33" s="6">
-        <v>3</v>
-      </c>
-      <c r="D33" s="6">
-        <v>140000</v>
-      </c>
-      <c r="E33" s="6">
-        <v>420000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>639</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C34" s="6">
-        <v>1</v>
-      </c>
-      <c r="D34" s="6">
-        <v>80000</v>
-      </c>
-      <c r="E34" s="6">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>639</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1</v>
-      </c>
-      <c r="D35" s="6">
-        <v>150000</v>
-      </c>
-      <c r="E35" s="6">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>640</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2</v>
-      </c>
-      <c r="D36" s="6">
-        <v>95000</v>
-      </c>
-      <c r="E36" s="6">
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
-        <v>640</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C37" s="6">
-        <v>4</v>
-      </c>
-      <c r="D37" s="6">
-        <v>220000</v>
-      </c>
-      <c r="E37" s="6">
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
-        <v>641</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C38" s="6">
-        <v>1</v>
-      </c>
-      <c r="D38" s="6">
-        <v>65000</v>
-      </c>
-      <c r="E38" s="6">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>641</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C39" s="6">
-        <v>1</v>
-      </c>
-      <c r="D39" s="6">
-        <v>150000</v>
-      </c>
-      <c r="E39" s="6">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="C40" s="6">
-        <v>2</v>
-      </c>
-      <c r="D40" s="6">
-        <v>840000</v>
-      </c>
-      <c r="E40" s="6">
-        <v>1680000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>643</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C41" s="6">
-        <v>1</v>
-      </c>
-      <c r="D41" s="6">
-        <v>125000</v>
-      </c>
-      <c r="E41" s="6">
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>643</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1</v>
-      </c>
-      <c r="D42" s="6">
-        <v>190000</v>
-      </c>
-      <c r="E42" s="6">
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>643</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="C43" s="6">
-        <v>2</v>
-      </c>
-      <c r="D43" s="6">
-        <v>300000</v>
-      </c>
-      <c r="E43" s="6">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
-        <v>644</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C44" s="6">
-        <v>2</v>
-      </c>
-      <c r="D44" s="6">
-        <v>130000</v>
-      </c>
-      <c r="E44" s="6">
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>645</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1</v>
-      </c>
-      <c r="D45" s="6">
-        <v>90000</v>
-      </c>
-      <c r="E45" s="6">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>645</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C46" s="6">
-        <v>1</v>
-      </c>
-      <c r="D46" s="23">
-        <v>240000</v>
-      </c>
-      <c r="E46" s="6">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>645</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1</v>
-      </c>
-      <c r="D47" s="6">
-        <v>135000</v>
-      </c>
-      <c r="E47" s="6">
-        <v>135000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" s="6">
-        <v>2</v>
-      </c>
-      <c r="D48" s="6">
-        <v>125000</v>
-      </c>
-      <c r="E48" s="6">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C49" s="6">
-        <v>1</v>
-      </c>
-      <c r="D49" s="6">
-        <v>95000</v>
-      </c>
-      <c r="E49" s="6">
-        <v>95000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C50" s="6">
-        <v>2</v>
-      </c>
-      <c r="D50" s="6">
-        <v>120000</v>
-      </c>
-      <c r="E50" s="6">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C51" s="6">
-        <v>1</v>
-      </c>
-      <c r="D51" s="6">
-        <v>90000</v>
-      </c>
-      <c r="E51" s="6">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C52" s="6">
-        <v>1</v>
-      </c>
-      <c r="D52" s="6">
-        <v>180000</v>
-      </c>
-      <c r="E52" s="6">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C53" s="6">
-        <v>1</v>
-      </c>
-      <c r="D53" s="6">
-        <v>75000</v>
-      </c>
-      <c r="E53" s="6">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C54" s="6">
-        <v>2</v>
-      </c>
-      <c r="D54" s="6">
-        <v>130000</v>
-      </c>
-      <c r="E54" s="6">
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1</v>
-      </c>
-      <c r="D55" s="6">
-        <v>135000</v>
-      </c>
-      <c r="E55" s="6">
-        <v>135000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C56" s="6">
-        <v>3</v>
-      </c>
-      <c r="D56" s="6">
-        <v>140000</v>
-      </c>
-      <c r="E56" s="6">
-        <v>420000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C57" s="6">
-        <v>1</v>
-      </c>
-      <c r="D57" s="6">
-        <v>80000</v>
-      </c>
-      <c r="E57" s="6">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C58" s="6">
-        <v>1</v>
-      </c>
-      <c r="D58" s="6">
-        <v>150000</v>
-      </c>
-      <c r="E58" s="6">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>650</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C59" s="6">
-        <v>2</v>
-      </c>
-      <c r="D59" s="6">
-        <v>95000</v>
-      </c>
-      <c r="E59" s="6">
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
-        <v>650</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C60" s="6">
-        <v>4</v>
-      </c>
-      <c r="D60" s="6">
-        <v>220000</v>
-      </c>
-      <c r="E60" s="6">
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>651</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C61" s="6">
-        <v>1</v>
-      </c>
-      <c r="D61" s="6">
-        <v>65000</v>
-      </c>
-      <c r="E61" s="6">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
-        <v>651</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C62" s="6">
-        <v>1</v>
-      </c>
-      <c r="D62" s="6">
-        <v>150000</v>
-      </c>
-      <c r="E62" s="6">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>652</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="C63" s="6">
-        <v>2</v>
-      </c>
-      <c r="D63" s="6">
-        <v>840000</v>
-      </c>
-      <c r="E63" s="6">
-        <v>1680000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C64" s="6">
-        <v>1</v>
-      </c>
-      <c r="D64" s="6">
-        <v>125000</v>
-      </c>
-      <c r="E64" s="6">
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C65" s="6">
-        <v>1</v>
-      </c>
-      <c r="D65" s="6">
-        <v>190000</v>
-      </c>
-      <c r="E65" s="6">
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="C66" s="6">
-        <v>2</v>
-      </c>
-      <c r="D66" s="6">
-        <v>300000</v>
-      </c>
-      <c r="E66" s="6">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C67" s="6">
-        <v>2</v>
-      </c>
-      <c r="D67" s="6">
-        <v>130000</v>
-      </c>
-      <c r="E67" s="6">
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>655</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C68" s="6">
-        <v>1</v>
-      </c>
-      <c r="D68" s="6">
-        <v>90000</v>
-      </c>
-      <c r="E68" s="6">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
-        <v>655</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C69" s="6">
-        <v>1</v>
-      </c>
-      <c r="D69" s="23">
-        <v>240000</v>
-      </c>
-      <c r="E69" s="6">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>655</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C70" s="6">
-        <v>1</v>
-      </c>
-      <c r="D70" s="6">
-        <v>135000</v>
-      </c>
-      <c r="E70" s="6">
         <v>135000</v>
       </c>
     </row>
@@ -8330,7 +7598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DCC079C-EA19-4A9E-9B67-86AE61784BF1}">
   <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8342,13 +7610,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -8356,7 +7624,7 @@
         <v>579</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
@@ -8686,7 +7954,7 @@
         <v>585</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C32" s="6">
         <v>2</v>

--- a/QuanLyNhaHang.xlsx
+++ b/QuanLyNhaHang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐỒ ÁN IT008\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCE9A63-F73C-4A7B-82A5-FA0107CD4B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFD2386-CA10-4C4F-8F44-364C8149A075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="KhachHang" sheetId="1" r:id="rId1"/>
@@ -949,12 +949,6 @@
     <t>lẩu sukiyaki.jpg</t>
   </si>
   <si>
-    <t>lẩu sườn sụn kim chi chi.jpg</t>
-  </si>
-  <si>
-    <t>lẩu thái hải sản sản.jpg</t>
-  </si>
-  <si>
     <t>lẩu cá bớp măng chua.jfif</t>
   </si>
   <si>
@@ -1939,9 +1933,6 @@
     <t>combo_nhom_nho_2.jpg</t>
   </si>
   <si>
-    <t>combo_nhom_nho_1</t>
-  </si>
-  <si>
     <t>TagTinhChat</t>
   </si>
   <si>
@@ -2306,6 +2297,15 @@
   </si>
   <si>
     <t>Đại Tiệc VIP (Giảm 500k)</t>
+  </si>
+  <si>
+    <t>lẩu thái hải sản.jpg</t>
+  </si>
+  <si>
+    <t>lẩu sườn sụn kim chi.jpg</t>
+  </si>
+  <si>
+    <t>combo_nhom_nho_1.png</t>
   </si>
 </sst>
 </file>
@@ -3430,7 +3430,7 @@
         <v>92</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>68</v>
@@ -3546,10 +3546,10 @@
         <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>14</v>
@@ -3572,10 +3572,10 @@
         <v>137</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G2" s="6">
         <v>75000</v>
@@ -3598,10 +3598,10 @@
         <v>138</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G3" s="6">
         <v>125000</v>
@@ -3624,10 +3624,10 @@
         <v>139</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G4" s="6">
         <v>65000</v>
@@ -3650,10 +3650,10 @@
         <v>140</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G5" s="6">
         <v>80000</v>
@@ -3676,10 +3676,10 @@
         <v>141</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G6" s="6">
         <v>95000</v>
@@ -3702,10 +3702,10 @@
         <v>142</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G7" s="6">
         <v>90000</v>
@@ -3722,16 +3722,16 @@
         <v>124</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D8" s="26" t="s">
         <v>143</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G8" s="6">
         <v>145000</v>
@@ -3754,10 +3754,10 @@
         <v>144</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G9" s="6">
         <v>120000</v>
@@ -3780,10 +3780,10 @@
         <v>145</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G10" s="6">
         <v>135000</v>
@@ -3806,10 +3806,10 @@
         <v>146</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="G11" s="6">
         <v>100000</v>
@@ -3832,10 +3832,10 @@
         <v>147</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G12" s="6">
         <v>150000</v>
@@ -3858,10 +3858,10 @@
         <v>148</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G13" s="6">
         <v>100000</v>
@@ -3884,10 +3884,10 @@
         <v>149</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G14" s="6">
         <v>130000</v>
@@ -3910,10 +3910,10 @@
         <v>150</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G15" s="6">
         <v>90000</v>
@@ -3930,16 +3930,16 @@
         <v>132</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D16" s="26" t="s">
         <v>151</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="G16" s="6">
         <v>120000</v>
@@ -3956,16 +3956,16 @@
         <v>133</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>152</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G17" s="6">
         <v>95000</v>
@@ -3988,10 +3988,10 @@
         <v>153</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G18" s="6">
         <v>110000</v>
@@ -4014,10 +4014,10 @@
         <v>154</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G19" s="6">
         <v>95000</v>
@@ -4040,10 +4040,10 @@
         <v>155</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G20" s="6">
         <v>100000</v>
@@ -4066,10 +4066,10 @@
         <v>156</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G21" s="6">
         <v>85000</v>
@@ -4092,10 +4092,10 @@
         <v>207</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G22" s="7">
         <v>135000</v>
@@ -4118,10 +4118,10 @@
         <v>208</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G23" s="7">
         <v>220000</v>
@@ -4144,10 +4144,10 @@
         <v>209</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G24" s="7">
         <v>120000</v>
@@ -4170,10 +4170,10 @@
         <v>210</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G25" s="7">
         <v>140000</v>
@@ -4196,10 +4196,10 @@
         <v>211</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G26" s="7">
         <v>180000</v>
@@ -4222,10 +4222,10 @@
         <v>212</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="G27" s="7">
         <v>210000</v>
@@ -4248,10 +4248,10 @@
         <v>213</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="G28" s="7">
         <v>190000</v>
@@ -4274,10 +4274,10 @@
         <v>247</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G29" s="7">
         <v>175000</v>
@@ -4300,10 +4300,10 @@
         <v>249</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="G30" s="7">
         <v>200000</v>
@@ -4326,10 +4326,10 @@
         <v>214</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="G31" s="7">
         <v>110000</v>
@@ -4352,10 +4352,10 @@
         <v>215</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="G32" s="7">
         <v>95000</v>
@@ -4378,10 +4378,10 @@
         <v>216</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G33" s="7">
         <v>85000</v>
@@ -4404,10 +4404,10 @@
         <v>217</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G34" s="7">
         <v>90000</v>
@@ -4430,10 +4430,10 @@
         <v>218</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G35" s="7">
         <v>130000</v>
@@ -4456,10 +4456,10 @@
         <v>219</v>
       </c>
       <c r="E36" s="28" t="s">
+        <v>664</v>
+      </c>
+      <c r="F36" s="28" t="s">
         <v>667</v>
-      </c>
-      <c r="F36" s="28" t="s">
-        <v>670</v>
       </c>
       <c r="G36" s="7">
         <v>100000</v>
@@ -4482,10 +4482,10 @@
         <v>282</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="G37" s="7">
         <v>250000</v>
@@ -4502,16 +4502,16 @@
         <v>257</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>305</v>
+        <v>756</v>
       </c>
       <c r="D38" s="27" t="s">
         <v>283</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G38" s="7">
         <v>270000</v>
@@ -4534,10 +4534,10 @@
         <v>284</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="G39" s="7">
         <v>230000</v>
@@ -4560,10 +4560,10 @@
         <v>285</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="G40" s="7">
         <v>290000</v>
@@ -4580,16 +4580,16 @@
         <v>260</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>306</v>
+        <v>755</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>286</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="G41" s="7">
         <v>280000</v>
@@ -4606,16 +4606,16 @@
         <v>261</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D42" s="27" t="s">
         <v>287</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="G42" s="7">
         <v>240000</v>
@@ -4638,10 +4638,10 @@
         <v>288</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="G43" s="7">
         <v>300000</v>
@@ -4658,16 +4658,16 @@
         <v>262</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D44" s="27" t="s">
         <v>289</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="G44" s="7">
         <v>190000</v>
@@ -4690,10 +4690,10 @@
         <v>290</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="G45" s="7">
         <v>195000</v>
@@ -4716,10 +4716,10 @@
         <v>291</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G46" s="7">
         <v>350000</v>
@@ -4736,16 +4736,16 @@
         <v>265</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>292</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G47" s="7">
         <v>330000</v>
@@ -4768,10 +4768,10 @@
         <v>295</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F48" s="28" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="G48" s="7">
         <v>379000</v>
@@ -4788,16 +4788,16 @@
         <v>296</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>297</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F49" s="32" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="G49" s="16">
         <v>500000</v>
@@ -4811,19 +4811,19 @@
         <v>279</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G50" s="17">
         <v>79000</v>
@@ -4837,19 +4837,19 @@
         <v>280</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F51" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G51" s="17">
         <v>69000</v>
@@ -4863,19 +4863,19 @@
         <v>281</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D52" s="30" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E52" s="28" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F52" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G52" s="17">
         <v>59000</v>
@@ -4886,22 +4886,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G53" s="17">
         <v>69000</v>
@@ -4912,22 +4912,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E54" s="28" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G54" s="14">
         <v>55000</v>
@@ -4938,22 +4938,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="G55" s="17">
         <v>45000</v>
@@ -4964,22 +4964,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="F56" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G56" s="17">
         <v>59000</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="G57" s="17">
         <v>65000</v>
@@ -5016,22 +5016,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F58" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G58" s="17">
         <v>79000</v>
@@ -5042,22 +5042,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G59" s="17">
         <v>69000</v>
@@ -5068,22 +5068,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F60" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G60" s="14">
         <v>65000</v>
@@ -5094,22 +5094,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F61" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G61" s="17">
         <v>45000</v>
@@ -5120,22 +5120,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D62" s="30" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="F62" s="28" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="G62" s="17">
         <v>69000</v>
@@ -5146,22 +5146,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F63" s="28" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="G63" s="17">
         <v>55000</v>
@@ -5172,22 +5172,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E64" s="28" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F64" s="28" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="G64" s="14">
         <v>49000</v>
@@ -5198,22 +5198,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F65" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G65" s="6">
         <v>60000</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F66" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G66" s="6">
         <v>65000</v>
@@ -5250,22 +5250,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E67" s="32" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G67" s="6">
         <v>45000</v>
@@ -5276,22 +5276,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="F68" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G68" s="6">
         <v>55000</v>
@@ -5302,22 +5302,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F69" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G69" s="6">
         <v>40000</v>
@@ -5328,22 +5328,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="F70" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G70" s="6">
         <v>45000</v>
@@ -5354,22 +5354,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F71" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G71" s="6">
         <v>38000</v>
@@ -5380,22 +5380,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="F72" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G72" s="6">
         <v>20000</v>
@@ -5406,22 +5406,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="F73" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G73" s="6">
         <v>30000</v>
@@ -5432,22 +5432,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E74" s="28" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="F74" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G74" s="6">
         <v>30000</v>
@@ -5458,22 +5458,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E75" s="28" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F75" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G75" s="6">
         <v>30000</v>
@@ -5484,22 +5484,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D76" s="26" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F76" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G76" s="6">
         <v>30000</v>
@@ -5510,22 +5510,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E77" s="28" t="s">
+        <v>690</v>
+      </c>
+      <c r="F77" s="28" t="s">
         <v>693</v>
-      </c>
-      <c r="F77" s="28" t="s">
-        <v>696</v>
       </c>
       <c r="G77" s="6">
         <v>160000</v>
@@ -5536,22 +5536,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E78" s="28" t="s">
+        <v>690</v>
+      </c>
+      <c r="F78" s="28" t="s">
         <v>693</v>
-      </c>
-      <c r="F78" s="28" t="s">
-        <v>696</v>
       </c>
       <c r="G78" s="6">
         <v>180000</v>
@@ -5562,22 +5562,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E79" s="28" t="s">
+        <v>690</v>
+      </c>
+      <c r="F79" s="28" t="s">
         <v>693</v>
-      </c>
-      <c r="F79" s="28" t="s">
-        <v>696</v>
       </c>
       <c r="G79" s="6">
         <v>170000</v>
@@ -5588,22 +5588,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D80" s="26" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E80" s="28" t="s">
+        <v>690</v>
+      </c>
+      <c r="F80" s="28" t="s">
         <v>693</v>
-      </c>
-      <c r="F80" s="28" t="s">
-        <v>696</v>
       </c>
       <c r="G80" s="6">
         <v>220000</v>
@@ -5614,22 +5614,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D81" s="26" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G81" s="6">
         <v>100000</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D82" s="26" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F82" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G82" s="6">
         <v>90000</v>
@@ -5666,22 +5666,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E83" s="28" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F83" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G83" s="6">
         <v>85000</v>
@@ -5692,22 +5692,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D84" s="26" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E84" s="28" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F84" s="28" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="G84" s="6">
         <v>130000</v>
@@ -5718,22 +5718,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E85" s="28" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F85" s="28" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="G85" s="6">
         <v>125000</v>
@@ -5744,22 +5744,22 @@
     </row>
     <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F86" s="28" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="G86" s="6">
         <v>200000</v>
@@ -5770,22 +5770,22 @@
     </row>
     <row r="87" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D87" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G87" s="6">
         <v>30000</v>
@@ -5796,22 +5796,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F88" s="28" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="G88" s="18">
         <v>35000</v>
@@ -5822,22 +5822,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D89" s="26" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F89" s="28" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G89" s="6">
         <v>70000</v>
@@ -5848,22 +5848,22 @@
     </row>
     <row r="90" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E90" s="28" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="F90" s="28" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G90" s="6">
         <v>25000</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="91" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D91" s="26" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G91" s="6">
         <v>70000</v>
@@ -5900,22 +5900,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E92" s="28" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="F92" s="28" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G92" s="6">
         <v>85000</v>
@@ -5926,22 +5926,22 @@
     </row>
     <row r="93" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D93" s="30" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E93" s="28" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="F93" s="28" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G93" s="18">
         <v>60000</v>
@@ -5952,22 +5952,22 @@
     </row>
     <row r="94" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B94" s="20" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D94" s="31" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="G94" s="9">
         <v>45000</v>
@@ -5978,22 +5978,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D95" s="26" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E95" s="28" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F95" s="28" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="G95" s="6">
         <v>50000</v>
@@ -6004,22 +6004,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D96" s="30" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F96" s="28" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="G96" s="6">
         <v>65000</v>
@@ -6030,22 +6030,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D97" s="26" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E97" s="28" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F97" s="28" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="G97" s="6">
         <v>50000</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D98" s="26" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E98" s="28" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F98" s="28" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G98" s="6">
         <v>55000</v>
@@ -6082,22 +6082,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D99" s="26" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E99" s="28" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F99" s="28" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G99" s="6">
         <v>65000</v>
@@ -6108,22 +6108,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D100" s="26" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E100" s="28" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F100" s="28" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G100" s="6">
         <v>85000</v>
@@ -6134,22 +6134,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D101" s="26" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F101" s="28" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="G101" s="17">
         <v>5000</v>
@@ -6160,22 +6160,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D102" s="30" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="F102" s="28" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="G102" s="17">
         <v>8000</v>
@@ -6186,22 +6186,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="F103" s="28" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="G103" s="14">
         <v>15000</v>
@@ -6212,22 +6212,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D104" s="26" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="F104" s="28" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="G104" s="14">
         <v>12000</v>
@@ -6238,22 +6238,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D105" s="26" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="F105" s="28" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="G105" s="14">
         <v>10000</v>
@@ -6264,22 +6264,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D106" s="26" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E106" s="28" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="F106" s="28" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="G106" s="14">
         <v>10000</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E107" s="28" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F107" s="28" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="G107" s="14">
         <v>8000</v>
@@ -6316,22 +6316,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D108" s="26" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E108" s="28" t="s">
+        <v>702</v>
+      </c>
+      <c r="F108" s="28" t="s">
         <v>705</v>
-      </c>
-      <c r="F108" s="28" t="s">
-        <v>708</v>
       </c>
       <c r="G108" s="17">
         <v>12000</v>
@@ -6342,22 +6342,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F109" s="28" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="G109" s="17">
         <v>10000</v>
@@ -6368,22 +6368,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D110" s="26" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F110" s="28" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="G110" s="17">
         <v>10000</v>
@@ -6394,22 +6394,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D111" s="26" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E111" s="28" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="F111" s="28" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="G111" s="17">
         <v>8000</v>
@@ -6420,22 +6420,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E112" s="28" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="F112" s="28" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="G112" s="17">
         <v>12000</v>
@@ -6446,22 +6446,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D113" s="30" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E113" s="28" t="s">
+        <v>702</v>
+      </c>
+      <c r="F113" s="28" t="s">
         <v>705</v>
-      </c>
-      <c r="F113" s="28" t="s">
-        <v>708</v>
       </c>
       <c r="G113" s="17">
         <v>12000</v>
@@ -6472,22 +6472,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D114" s="30" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="F114" s="28" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="G114" s="17">
         <v>15000</v>
@@ -6498,16 +6498,16 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D115" s="30" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E115" s="28"/>
       <c r="F115" s="28"/>
@@ -6520,16 +6520,16 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D116" s="26" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E116" s="28"/>
       <c r="F116" s="28"/>
@@ -6542,16 +6542,16 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D117" s="26" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E117" s="28"/>
       <c r="F117" s="28"/>
@@ -6564,16 +6564,16 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>635</v>
+        <v>757</v>
       </c>
       <c r="D118" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E118" s="28"/>
       <c r="F118" s="28"/>
@@ -6586,16 +6586,16 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D119" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E119" s="28"/>
       <c r="F119" s="28"/>
@@ -6608,16 +6608,16 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D120" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E120" s="28"/>
       <c r="F120" s="28"/>
@@ -6630,16 +6630,16 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D121" s="26" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E121" s="28"/>
       <c r="F121" s="28"/>
@@ -6652,16 +6652,16 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>573</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="D122" s="26" t="s">
         <v>586</v>
-      </c>
-      <c r="B122" s="19" t="s">
-        <v>575</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>631</v>
-      </c>
-      <c r="D122" s="26" t="s">
-        <v>588</v>
       </c>
       <c r="E122" s="28"/>
       <c r="F122" s="28"/>
@@ -6674,16 +6674,16 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D123" s="26" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E123" s="28"/>
       <c r="F123" s="28"/>
@@ -6728,19 +6728,19 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
@@ -6751,7 +6751,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>47</v>
@@ -6760,10 +6760,10 @@
         <v>31</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>50</v>
@@ -6783,7 +6783,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>39</v>
@@ -6792,10 +6792,10 @@
         <v>23</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>34</v>
@@ -6815,7 +6815,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>41</v>
@@ -6824,10 +6824,10 @@
         <v>23</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>51</v>
@@ -6847,7 +6847,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -6856,10 +6856,10 @@
         <v>25</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>53</v>
@@ -6879,7 +6879,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>43</v>
@@ -6888,10 +6888,10 @@
         <v>27</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>54</v>
@@ -6911,7 +6911,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>48</v>
@@ -6920,10 +6920,10 @@
         <v>21</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>55</v>
@@ -6943,7 +6943,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>43</v>
@@ -6952,10 +6952,10 @@
         <v>33</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>56</v>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>39</v>
@@ -6984,10 +6984,10 @@
         <v>21</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>57</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>48</v>
@@ -7016,10 +7016,10 @@
         <v>33</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>58</v>
@@ -7039,7 +7039,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>49</v>
@@ -7048,10 +7048,10 @@
         <v>21</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>59</v>
@@ -7089,21 +7089,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>749</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B2" s="33">
         <v>50</v>
@@ -7117,7 +7117,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B3" s="33">
         <v>400</v>
@@ -7131,7 +7131,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B4" s="33">
         <v>750</v>
@@ -7145,7 +7145,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B5" s="33">
         <v>150</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B6" s="33">
         <v>3000</v>
@@ -7196,7 +7196,7 @@
         <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -7204,7 +7204,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>159</v>
@@ -7221,7 +7221,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>175</v>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>165</v>
@@ -7255,7 +7255,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>171</v>
@@ -7272,7 +7272,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>225</v>
@@ -7289,7 +7289,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>119</v>
@@ -7306,7 +7306,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>170</v>
@@ -7323,7 +7323,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>166</v>
@@ -7340,7 +7340,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>224</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>161</v>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>168</v>
@@ -7391,7 +7391,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>162</v>
@@ -7408,7 +7408,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>222</v>
@@ -7425,7 +7425,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>160</v>
@@ -7442,7 +7442,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>168</v>
@@ -7459,10 +7459,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C17" s="6">
         <v>2</v>
@@ -7476,7 +7476,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>159</v>
@@ -7493,7 +7493,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>227</v>
@@ -7510,7 +7510,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>272</v>
@@ -7527,7 +7527,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>171</v>
@@ -7544,7 +7544,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>170</v>
@@ -7561,7 +7561,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>271</v>
@@ -7578,7 +7578,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>166</v>
@@ -7621,7 +7621,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>119</v>
@@ -7632,7 +7632,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>225</v>
@@ -7643,7 +7643,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>268</v>
@@ -7654,10 +7654,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>160</v>
@@ -7676,7 +7676,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>224</v>
@@ -7687,7 +7687,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>267</v>
@@ -7698,10 +7698,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -7709,7 +7709,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>164</v>
@@ -7720,7 +7720,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>226</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>270</v>
@@ -7742,7 +7742,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>279</v>
@@ -7753,7 +7753,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>161</v>
@@ -7764,7 +7764,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>166</v>
@@ -7775,7 +7775,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>229</v>
@@ -7786,7 +7786,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>223</v>
@@ -7797,7 +7797,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>269</v>
@@ -7808,10 +7808,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C19" s="6">
         <v>2</v>
@@ -7819,7 +7819,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>162</v>
@@ -7830,7 +7830,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>165</v>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>222</v>
@@ -7852,7 +7852,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>226</v>
@@ -7863,7 +7863,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>266</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C25" s="6">
         <v>2</v>
@@ -7885,7 +7885,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>160</v>
@@ -7896,7 +7896,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>164</v>
@@ -7907,7 +7907,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>225</v>
@@ -7918,7 +7918,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>228</v>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>270</v>
@@ -7940,7 +7940,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>279</v>
@@ -7951,7 +7951,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>119</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>167</v>
@@ -7973,7 +7973,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>222</v>
@@ -7984,7 +7984,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>221</v>
@@ -7995,7 +7995,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>228</v>
@@ -8006,7 +8006,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>277</v>
@@ -8017,10 +8017,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C38" s="6">
         <v>2</v>
@@ -8028,7 +8028,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>280</v>
@@ -8039,7 +8039,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>160</v>
@@ -8050,7 +8050,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>164</v>
@@ -8061,7 +8061,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>224</v>
@@ -8072,7 +8072,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>227</v>
@@ -8083,7 +8083,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>223</v>
@@ -8094,7 +8094,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>276</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C46" s="6">
         <v>2</v>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>279</v>
@@ -8127,7 +8127,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>159</v>
@@ -8138,7 +8138,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>175</v>
@@ -8149,7 +8149,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>225</v>
@@ -8160,7 +8160,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>222</v>
@@ -8171,7 +8171,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>226</v>
@@ -8182,7 +8182,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>278</v>
@@ -8193,10 +8193,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C54" s="6">
         <v>2</v>

--- a/QuanLyNhaHang.xlsx
+++ b/QuanLyNhaHang.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐỒ ÁN IT008\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMINIS\Documents\QuanLyDatMonNhaHang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFD2386-CA10-4C4F-8F44-364C8149A075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199CC3CD-0F83-459E-B135-57F53584852B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="764">
   <si>
     <t>MaKH</t>
   </si>
@@ -1759,12 +1759,6 @@
     <t>ComBo Nhóm Lớn 3</t>
   </si>
   <si>
-    <t>1-2 người</t>
-  </si>
-  <si>
-    <t>2-4 người</t>
-  </si>
-  <si>
     <t>M114</t>
   </si>
   <si>
@@ -1792,9 +1786,6 @@
     <t>M122</t>
   </si>
   <si>
-    <t>5-8 người</t>
-  </si>
-  <si>
     <t>GiamGia</t>
   </si>
   <si>
@@ -2306,6 +2297,42 @@
   </si>
   <si>
     <t>combo_nhom_nho_1.png</t>
+  </si>
+  <si>
+    <t>Súp gà nấm, Vịt quay sốt cam, Lẩu gà lá giang, Chè khúc bạch 
+ 1-2 người</t>
+  </si>
+  <si>
+    <t>Súp bí đỏ, Heo cuộn phô mai đút lò, Lẩu sườn sụn kim chi, Kem xoài nhiệt đới
+1-2 người</t>
+  </si>
+  <si>
+    <t>Salad rong biển &amp; trứng cua, Cá hồi áp chảo sốt bơ chanh, Lẩu thái hải sản, Dĩa trái cây tổng hợp
+1-2 người</t>
+  </si>
+  <si>
+    <t>Súp ngô kem, Salad cá ngừ, Gà nướng mật ong và thảo mộc, Cua lột chiên giòn ăn kèm gỏi xoài xanh, Lẩu dê thuốc bắc, Chè hạt sen long nhãn
+2-4 người</t>
+  </si>
+  <si>
+    <t>Súp cua trứng bắc thảo, Gỏi củ hủ dừa tôm thịt, Sườn cừu nướng sốt rượu vang đỏ, Cá hồi áp chảo sốt bơ chanh, Lẩu bò sa tế, Kem dừa xiêm
+2-4 người</t>
+  </si>
+  <si>
+    <t>Súp bí đỏ, Salad rong biển &amp; trứng cua, Vịt quay sốt cam, Mực nhồi thịt sốt cà chua, Lẩu thái hải sản, Dĩa trái cây tổng hợp
+2-4 người</t>
+  </si>
+  <si>
+    <t>Súp gà nấm, Gỏi xoài tôm khô, Bò lúc lắc khoai tây chiên, Sườn cừu nướng sốt rượu vang đỏ, Mực nhồi thịt sốt cà chua, Lẩu Sukiyaki, Dưa lưới lạnh, Chè bưởi
+5-8 người</t>
+  </si>
+  <si>
+    <t>Súp bí đỏ, Salad rong biển &amp; trứng cua, Gà nướng mật ong và thảo mộc, Heo cuộn phô mai đút lò, Tôm càng nướng muối ớt, Lẩu thập cẩm đặc biệt, Dĩa trái cây tổng hợp, Kem xoài nhiệt đới
+5-8 người</t>
+  </si>
+  <si>
+    <t>Súp hải sản, Cuốn diếp tôm thịt, Sườn cừu nướng sốt rượu vang đỏ, Vịt quay sốt cam, Cá hồi áp chảo sốt bơ chanh, Lẩu Nấm Truffle Kem Sữa, Chè khúc bạch
+5-8 người</t>
   </si>
 </sst>
 </file>
@@ -2485,7 +2512,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2580,6 +2607,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3525,7 +3555,7 @@
   <cols>
     <col min="2" max="2" width="39.109375" customWidth="1"/>
     <col min="3" max="3" width="34.44140625" customWidth="1"/>
-    <col min="4" max="4" width="64.5546875" customWidth="1"/>
+    <col min="4" max="4" width="84.21875" customWidth="1"/>
     <col min="5" max="5" width="28.77734375" customWidth="1"/>
     <col min="6" max="6" width="28.88671875" customWidth="1"/>
     <col min="7" max="7" width="16.88671875" customWidth="1"/>
@@ -3546,10 +3576,10 @@
         <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>14</v>
@@ -3572,10 +3602,10 @@
         <v>137</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G2" s="6">
         <v>75000</v>
@@ -3598,10 +3628,10 @@
         <v>138</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G3" s="6">
         <v>125000</v>
@@ -3624,10 +3654,10 @@
         <v>139</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G4" s="6">
         <v>65000</v>
@@ -3650,10 +3680,10 @@
         <v>140</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G5" s="6">
         <v>80000</v>
@@ -3676,10 +3706,10 @@
         <v>141</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G6" s="6">
         <v>95000</v>
@@ -3702,10 +3732,10 @@
         <v>142</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="G7" s="6">
         <v>90000</v>
@@ -3722,16 +3752,16 @@
         <v>124</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D8" s="26" t="s">
         <v>143</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="G8" s="6">
         <v>145000</v>
@@ -3754,10 +3784,10 @@
         <v>144</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="G9" s="6">
         <v>120000</v>
@@ -3780,10 +3810,10 @@
         <v>145</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="G10" s="6">
         <v>135000</v>
@@ -3806,10 +3836,10 @@
         <v>146</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G11" s="6">
         <v>100000</v>
@@ -3832,10 +3862,10 @@
         <v>147</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G12" s="6">
         <v>150000</v>
@@ -3858,10 +3888,10 @@
         <v>148</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G13" s="6">
         <v>100000</v>
@@ -3884,10 +3914,10 @@
         <v>149</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G14" s="6">
         <v>130000</v>
@@ -3910,10 +3940,10 @@
         <v>150</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G15" s="6">
         <v>90000</v>
@@ -3930,16 +3960,16 @@
         <v>132</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D16" s="26" t="s">
         <v>151</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="G16" s="6">
         <v>120000</v>
@@ -3956,16 +3986,16 @@
         <v>133</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>152</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G17" s="6">
         <v>95000</v>
@@ -3988,10 +4018,10 @@
         <v>153</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="G18" s="6">
         <v>110000</v>
@@ -4014,10 +4044,10 @@
         <v>154</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G19" s="6">
         <v>95000</v>
@@ -4040,10 +4070,10 @@
         <v>155</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="G20" s="6">
         <v>100000</v>
@@ -4066,10 +4096,10 @@
         <v>156</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G21" s="6">
         <v>85000</v>
@@ -4092,10 +4122,10 @@
         <v>207</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G22" s="7">
         <v>135000</v>
@@ -4118,10 +4148,10 @@
         <v>208</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G23" s="7">
         <v>220000</v>
@@ -4144,10 +4174,10 @@
         <v>209</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G24" s="7">
         <v>120000</v>
@@ -4170,10 +4200,10 @@
         <v>210</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G25" s="7">
         <v>140000</v>
@@ -4196,10 +4226,10 @@
         <v>211</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G26" s="7">
         <v>180000</v>
@@ -4222,10 +4252,10 @@
         <v>212</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="G27" s="7">
         <v>210000</v>
@@ -4248,10 +4278,10 @@
         <v>213</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G28" s="7">
         <v>190000</v>
@@ -4274,10 +4304,10 @@
         <v>247</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G29" s="7">
         <v>175000</v>
@@ -4300,10 +4330,10 @@
         <v>249</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G30" s="7">
         <v>200000</v>
@@ -4326,10 +4356,10 @@
         <v>214</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="G31" s="7">
         <v>110000</v>
@@ -4352,10 +4382,10 @@
         <v>215</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G32" s="7">
         <v>95000</v>
@@ -4378,10 +4408,10 @@
         <v>216</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G33" s="7">
         <v>85000</v>
@@ -4404,10 +4434,10 @@
         <v>217</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G34" s="7">
         <v>90000</v>
@@ -4430,10 +4460,10 @@
         <v>218</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G35" s="7">
         <v>130000</v>
@@ -4456,10 +4486,10 @@
         <v>219</v>
       </c>
       <c r="E36" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="F36" s="28" t="s">
         <v>664</v>
-      </c>
-      <c r="F36" s="28" t="s">
-        <v>667</v>
       </c>
       <c r="G36" s="7">
         <v>100000</v>
@@ -4482,10 +4512,10 @@
         <v>282</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="G37" s="7">
         <v>250000</v>
@@ -4502,16 +4532,16 @@
         <v>257</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D38" s="27" t="s">
         <v>283</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="G38" s="7">
         <v>270000</v>
@@ -4534,10 +4564,10 @@
         <v>284</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="G39" s="7">
         <v>230000</v>
@@ -4560,10 +4590,10 @@
         <v>285</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="G40" s="7">
         <v>290000</v>
@@ -4580,16 +4610,16 @@
         <v>260</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>286</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G41" s="7">
         <v>280000</v>
@@ -4612,10 +4642,10 @@
         <v>287</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G42" s="7">
         <v>240000</v>
@@ -4638,10 +4668,10 @@
         <v>288</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G43" s="7">
         <v>300000</v>
@@ -4664,10 +4694,10 @@
         <v>289</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="G44" s="7">
         <v>190000</v>
@@ -4690,10 +4720,10 @@
         <v>290</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="G45" s="7">
         <v>195000</v>
@@ -4716,10 +4746,10 @@
         <v>291</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="G46" s="7">
         <v>350000</v>
@@ -4742,10 +4772,10 @@
         <v>292</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="G47" s="7">
         <v>330000</v>
@@ -4768,10 +4798,10 @@
         <v>295</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F48" s="28" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="G48" s="7">
         <v>379000</v>
@@ -4794,10 +4824,10 @@
         <v>297</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="F49" s="32" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="G49" s="16">
         <v>500000</v>
@@ -4820,10 +4850,10 @@
         <v>352</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="G50" s="17">
         <v>79000</v>
@@ -4846,10 +4876,10 @@
         <v>324</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="F51" s="28" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="G51" s="17">
         <v>69000</v>
@@ -4872,10 +4902,10 @@
         <v>325</v>
       </c>
       <c r="E52" s="28" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F52" s="28" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="G52" s="17">
         <v>59000</v>
@@ -4898,10 +4928,10 @@
         <v>326</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="G53" s="17">
         <v>69000</v>
@@ -4924,10 +4954,10 @@
         <v>327</v>
       </c>
       <c r="E54" s="28" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="G54" s="14">
         <v>55000</v>
@@ -4950,10 +4980,10 @@
         <v>328</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="G55" s="17">
         <v>45000</v>
@@ -4976,10 +5006,10 @@
         <v>329</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F56" s="28" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="G56" s="17">
         <v>59000</v>
@@ -5002,10 +5032,10 @@
         <v>330</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="G57" s="17">
         <v>65000</v>
@@ -5028,10 +5058,10 @@
         <v>331</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F58" s="28" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="G58" s="17">
         <v>79000</v>
@@ -5054,10 +5084,10 @@
         <v>332</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="G59" s="17">
         <v>69000</v>
@@ -5080,10 +5110,10 @@
         <v>333</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F60" s="28" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="G60" s="14">
         <v>65000</v>
@@ -5106,10 +5136,10 @@
         <v>334</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F61" s="28" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="G61" s="17">
         <v>45000</v>
@@ -5132,10 +5162,10 @@
         <v>335</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F62" s="28" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="G62" s="17">
         <v>69000</v>
@@ -5158,10 +5188,10 @@
         <v>336</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F63" s="28" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="G63" s="17">
         <v>55000</v>
@@ -5184,10 +5214,10 @@
         <v>337</v>
       </c>
       <c r="E64" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F64" s="28" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="G64" s="14">
         <v>49000</v>
@@ -5210,10 +5240,10 @@
         <v>413</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="F65" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G65" s="6">
         <v>60000</v>
@@ -5236,10 +5266,10 @@
         <v>414</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F66" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G66" s="6">
         <v>65000</v>
@@ -5262,10 +5292,10 @@
         <v>415</v>
       </c>
       <c r="E67" s="32" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G67" s="6">
         <v>45000</v>
@@ -5288,10 +5318,10 @@
         <v>416</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F68" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G68" s="6">
         <v>55000</v>
@@ -5314,10 +5344,10 @@
         <v>417</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F69" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G69" s="6">
         <v>40000</v>
@@ -5340,10 +5370,10 @@
         <v>418</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="F70" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G70" s="6">
         <v>45000</v>
@@ -5366,10 +5396,10 @@
         <v>419</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F71" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G71" s="6">
         <v>38000</v>
@@ -5392,10 +5422,10 @@
         <v>420</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="F72" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G72" s="6">
         <v>20000</v>
@@ -5418,10 +5448,10 @@
         <v>421</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="F73" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G73" s="6">
         <v>30000</v>
@@ -5444,10 +5474,10 @@
         <v>422</v>
       </c>
       <c r="E74" s="28" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="F74" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G74" s="6">
         <v>30000</v>
@@ -5470,10 +5500,10 @@
         <v>423</v>
       </c>
       <c r="E75" s="28" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F75" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G75" s="6">
         <v>30000</v>
@@ -5496,10 +5526,10 @@
         <v>424</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F76" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G76" s="6">
         <v>30000</v>
@@ -5522,10 +5552,10 @@
         <v>425</v>
       </c>
       <c r="E77" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="F77" s="28" t="s">
         <v>690</v>
-      </c>
-      <c r="F77" s="28" t="s">
-        <v>693</v>
       </c>
       <c r="G77" s="6">
         <v>160000</v>
@@ -5548,10 +5578,10 @@
         <v>426</v>
       </c>
       <c r="E78" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="F78" s="28" t="s">
         <v>690</v>
-      </c>
-      <c r="F78" s="28" t="s">
-        <v>693</v>
       </c>
       <c r="G78" s="6">
         <v>180000</v>
@@ -5574,10 +5604,10 @@
         <v>427</v>
       </c>
       <c r="E79" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="F79" s="28" t="s">
         <v>690</v>
-      </c>
-      <c r="F79" s="28" t="s">
-        <v>693</v>
       </c>
       <c r="G79" s="6">
         <v>170000</v>
@@ -5600,10 +5630,10 @@
         <v>428</v>
       </c>
       <c r="E80" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="F80" s="28" t="s">
         <v>690</v>
-      </c>
-      <c r="F80" s="28" t="s">
-        <v>693</v>
       </c>
       <c r="G80" s="6">
         <v>220000</v>
@@ -5626,10 +5656,10 @@
         <v>429</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G81" s="6">
         <v>100000</v>
@@ -5652,10 +5682,10 @@
         <v>430</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F82" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G82" s="6">
         <v>90000</v>
@@ -5678,10 +5708,10 @@
         <v>431</v>
       </c>
       <c r="E83" s="28" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F83" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G83" s="6">
         <v>85000</v>
@@ -5704,10 +5734,10 @@
         <v>432</v>
       </c>
       <c r="E84" s="28" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="F84" s="28" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G84" s="6">
         <v>130000</v>
@@ -5730,10 +5760,10 @@
         <v>433</v>
       </c>
       <c r="E85" s="28" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="F85" s="28" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G85" s="6">
         <v>125000</v>
@@ -5756,10 +5786,10 @@
         <v>434</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="F86" s="28" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G86" s="6">
         <v>200000</v>
@@ -5782,10 +5812,10 @@
         <v>464</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="G87" s="6">
         <v>30000</v>
@@ -5808,10 +5838,10 @@
         <v>465</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F88" s="28" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="G88" s="18">
         <v>35000</v>
@@ -5834,10 +5864,10 @@
         <v>466</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F89" s="28" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G89" s="6">
         <v>70000</v>
@@ -5860,10 +5890,10 @@
         <v>467</v>
       </c>
       <c r="E90" s="28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="F90" s="28" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="G90" s="6">
         <v>25000</v>
@@ -5886,10 +5916,10 @@
         <v>468</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G91" s="6">
         <v>70000</v>
@@ -5912,10 +5942,10 @@
         <v>469</v>
       </c>
       <c r="E92" s="28" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="F92" s="28" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G92" s="6">
         <v>85000</v>
@@ -5938,10 +5968,10 @@
         <v>470</v>
       </c>
       <c r="E93" s="28" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F93" s="28" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G93" s="18">
         <v>60000</v>
@@ -5964,10 +5994,10 @@
         <v>471</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="G94" s="9">
         <v>45000</v>
@@ -5990,10 +6020,10 @@
         <v>484</v>
       </c>
       <c r="E95" s="28" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F95" s="28" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="G95" s="6">
         <v>50000</v>
@@ -6016,10 +6046,10 @@
         <v>486</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F96" s="28" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="G96" s="6">
         <v>65000</v>
@@ -6042,10 +6072,10 @@
         <v>488</v>
       </c>
       <c r="E97" s="28" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F97" s="28" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="G97" s="6">
         <v>50000</v>
@@ -6068,10 +6098,10 @@
         <v>489</v>
       </c>
       <c r="E98" s="28" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F98" s="28" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="G98" s="6">
         <v>55000</v>
@@ -6094,10 +6124,10 @@
         <v>481</v>
       </c>
       <c r="E99" s="28" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="F99" s="28" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="G99" s="6">
         <v>65000</v>
@@ -6120,10 +6150,10 @@
         <v>490</v>
       </c>
       <c r="E100" s="28" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F100" s="28" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="G100" s="6">
         <v>85000</v>
@@ -6146,10 +6176,10 @@
         <v>511</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F101" s="28" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G101" s="17">
         <v>5000</v>
@@ -6172,10 +6202,10 @@
         <v>512</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F102" s="28" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G102" s="17">
         <v>8000</v>
@@ -6198,10 +6228,10 @@
         <v>513</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F103" s="28" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G103" s="14">
         <v>15000</v>
@@ -6224,10 +6254,10 @@
         <v>514</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F104" s="28" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G104" s="14">
         <v>12000</v>
@@ -6250,10 +6280,10 @@
         <v>515</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="F105" s="28" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G105" s="14">
         <v>10000</v>
@@ -6276,10 +6306,10 @@
         <v>516</v>
       </c>
       <c r="E106" s="28" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="F106" s="28" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G106" s="14">
         <v>10000</v>
@@ -6302,10 +6332,10 @@
         <v>517</v>
       </c>
       <c r="E107" s="28" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F107" s="28" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G107" s="14">
         <v>8000</v>
@@ -6328,10 +6358,10 @@
         <v>518</v>
       </c>
       <c r="E108" s="28" t="s">
+        <v>699</v>
+      </c>
+      <c r="F108" s="28" t="s">
         <v>702</v>
-      </c>
-      <c r="F108" s="28" t="s">
-        <v>705</v>
       </c>
       <c r="G108" s="17">
         <v>12000</v>
@@ -6354,10 +6384,10 @@
         <v>524</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="F109" s="28" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G109" s="17">
         <v>10000</v>
@@ -6380,10 +6410,10 @@
         <v>519</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F110" s="28" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G110" s="17">
         <v>10000</v>
@@ -6406,10 +6436,10 @@
         <v>520</v>
       </c>
       <c r="E111" s="28" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="F111" s="28" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G111" s="17">
         <v>8000</v>
@@ -6432,10 +6462,10 @@
         <v>521</v>
       </c>
       <c r="E112" s="28" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="F112" s="28" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="G112" s="17">
         <v>12000</v>
@@ -6458,10 +6488,10 @@
         <v>509</v>
       </c>
       <c r="E113" s="28" t="s">
+        <v>699</v>
+      </c>
+      <c r="F113" s="28" t="s">
         <v>702</v>
-      </c>
-      <c r="F113" s="28" t="s">
-        <v>705</v>
       </c>
       <c r="G113" s="17">
         <v>12000</v>
@@ -6484,10 +6514,10 @@
         <v>523</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="F114" s="28" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="G114" s="17">
         <v>15000</v>
@@ -6496,18 +6526,18 @@
         <v>115</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B115" s="18" t="s">
         <v>566</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D115" s="30" t="s">
-        <v>575</v>
+        <v>755</v>
       </c>
       <c r="E115" s="28"/>
       <c r="F115" s="28"/>
@@ -6518,18 +6548,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B116" s="19" t="s">
         <v>569</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>626</v>
-      </c>
-      <c r="D116" s="26" t="s">
-        <v>575</v>
+        <v>623</v>
+      </c>
+      <c r="D116" s="34" t="s">
+        <v>756</v>
       </c>
       <c r="E116" s="28"/>
       <c r="F116" s="28"/>
@@ -6540,18 +6570,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>570</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>627</v>
-      </c>
-      <c r="D117" s="26" t="s">
-        <v>575</v>
+        <v>624</v>
+      </c>
+      <c r="D117" s="34" t="s">
+        <v>757</v>
       </c>
       <c r="E117" s="28"/>
       <c r="F117" s="28"/>
@@ -6562,18 +6592,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>567</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>757</v>
-      </c>
-      <c r="D118" s="26" t="s">
-        <v>576</v>
+        <v>754</v>
+      </c>
+      <c r="D118" s="34" t="s">
+        <v>758</v>
       </c>
       <c r="E118" s="28"/>
       <c r="F118" s="28"/>
@@ -6584,18 +6614,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B119" s="19" t="s">
         <v>571</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>632</v>
-      </c>
-      <c r="D119" s="26" t="s">
-        <v>576</v>
+        <v>629</v>
+      </c>
+      <c r="D119" s="34" t="s">
+        <v>759</v>
       </c>
       <c r="E119" s="28"/>
       <c r="F119" s="28"/>
@@ -6606,18 +6636,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B120" s="19" t="s">
         <v>572</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>631</v>
-      </c>
-      <c r="D120" s="26" t="s">
-        <v>576</v>
+        <v>628</v>
+      </c>
+      <c r="D120" s="34" t="s">
+        <v>760</v>
       </c>
       <c r="E120" s="28"/>
       <c r="F120" s="28"/>
@@ -6628,18 +6658,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B121" s="19" t="s">
         <v>568</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>628</v>
-      </c>
-      <c r="D121" s="26" t="s">
-        <v>586</v>
+        <v>625</v>
+      </c>
+      <c r="D121" s="34" t="s">
+        <v>761</v>
       </c>
       <c r="E121" s="28"/>
       <c r="F121" s="28"/>
@@ -6650,18 +6680,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B122" s="19" t="s">
         <v>573</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>629</v>
-      </c>
-      <c r="D122" s="26" t="s">
-        <v>586</v>
+        <v>626</v>
+      </c>
+      <c r="D122" s="34" t="s">
+        <v>762</v>
       </c>
       <c r="E122" s="28"/>
       <c r="F122" s="28"/>
@@ -6672,18 +6702,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B123" s="19" t="s">
         <v>574</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>630</v>
-      </c>
-      <c r="D123" s="26" t="s">
-        <v>586</v>
+        <v>627</v>
+      </c>
+      <c r="D123" s="34" t="s">
+        <v>763</v>
       </c>
       <c r="E123" s="28"/>
       <c r="F123" s="28"/>
@@ -6728,19 +6758,19 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
@@ -6751,7 +6781,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>47</v>
@@ -6760,10 +6790,10 @@
         <v>31</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>50</v>
@@ -6783,7 +6813,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>39</v>
@@ -6792,10 +6822,10 @@
         <v>23</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>34</v>
@@ -6815,7 +6845,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>41</v>
@@ -6824,10 +6854,10 @@
         <v>23</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>51</v>
@@ -6847,7 +6877,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -6856,10 +6886,10 @@
         <v>25</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>53</v>
@@ -6879,7 +6909,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>43</v>
@@ -6888,10 +6918,10 @@
         <v>27</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>54</v>
@@ -6911,7 +6941,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>48</v>
@@ -6920,10 +6950,10 @@
         <v>21</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>55</v>
@@ -6943,7 +6973,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>43</v>
@@ -6952,10 +6982,10 @@
         <v>33</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>56</v>
@@ -6975,7 +7005,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>39</v>
@@ -6984,10 +7014,10 @@
         <v>21</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>57</v>
@@ -7007,7 +7037,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>48</v>
@@ -7016,10 +7046,10 @@
         <v>33</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>58</v>
@@ -7039,7 +7069,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>49</v>
@@ -7048,10 +7078,10 @@
         <v>21</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>59</v>
@@ -7089,21 +7119,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B2" s="33">
         <v>50</v>
@@ -7117,7 +7147,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B3" s="33">
         <v>400</v>
@@ -7131,7 +7161,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B4" s="33">
         <v>750</v>
@@ -7145,7 +7175,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B5" s="33">
         <v>150</v>
@@ -7159,7 +7189,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B6" s="33">
         <v>3000</v>
@@ -7196,7 +7226,7 @@
         <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -7204,7 +7234,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>159</v>
@@ -7221,7 +7251,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>175</v>
@@ -7238,7 +7268,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>165</v>
@@ -7255,7 +7285,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>171</v>
@@ -7272,7 +7302,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>225</v>
@@ -7289,7 +7319,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>119</v>
@@ -7306,7 +7336,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>170</v>
@@ -7323,7 +7353,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>166</v>
@@ -7340,7 +7370,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>224</v>
@@ -7357,7 +7387,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>161</v>
@@ -7374,7 +7404,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>168</v>
@@ -7391,7 +7421,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>162</v>
@@ -7408,7 +7438,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>222</v>
@@ -7425,7 +7455,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>160</v>
@@ -7442,7 +7472,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>168</v>
@@ -7459,10 +7489,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C17" s="6">
         <v>2</v>
@@ -7476,7 +7506,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>159</v>
@@ -7493,7 +7523,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>227</v>
@@ -7510,7 +7540,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>272</v>
@@ -7527,7 +7557,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>171</v>
@@ -7544,7 +7574,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>170</v>
@@ -7561,7 +7591,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>271</v>
@@ -7578,7 +7608,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>166</v>
@@ -7621,7 +7651,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>119</v>
@@ -7632,7 +7662,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>225</v>
@@ -7643,7 +7673,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>268</v>
@@ -7654,7 +7684,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>339</v>
@@ -7665,7 +7695,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>160</v>
@@ -7676,7 +7706,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>224</v>
@@ -7687,7 +7717,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>267</v>
@@ -7698,7 +7728,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>345</v>
@@ -7709,7 +7739,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>164</v>
@@ -7720,7 +7750,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>226</v>
@@ -7731,7 +7761,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>270</v>
@@ -7742,7 +7772,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>279</v>
@@ -7753,7 +7783,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>161</v>
@@ -7764,7 +7794,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>166</v>
@@ -7775,7 +7805,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>229</v>
@@ -7786,7 +7816,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>223</v>
@@ -7797,7 +7827,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>269</v>
@@ -7808,7 +7838,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>340</v>
@@ -7819,7 +7849,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>162</v>
@@ -7830,7 +7860,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>165</v>
@@ -7841,7 +7871,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>222</v>
@@ -7852,7 +7882,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>226</v>
@@ -7863,7 +7893,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>266</v>
@@ -7874,7 +7904,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>343</v>
@@ -7885,7 +7915,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>160</v>
@@ -7896,7 +7926,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>164</v>
@@ -7907,7 +7937,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>225</v>
@@ -7918,7 +7948,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>228</v>
@@ -7929,7 +7959,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>270</v>
@@ -7940,7 +7970,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>279</v>
@@ -7951,7 +7981,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>119</v>
@@ -7962,7 +7992,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>167</v>
@@ -7973,7 +8003,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>222</v>
@@ -7984,7 +8014,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>221</v>
@@ -7995,7 +8025,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>228</v>
@@ -8006,7 +8036,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>277</v>
@@ -8017,7 +8047,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>342</v>
@@ -8028,7 +8058,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>280</v>
@@ -8039,7 +8069,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>160</v>
@@ -8050,7 +8080,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>164</v>
@@ -8061,7 +8091,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>224</v>
@@ -8072,7 +8102,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>227</v>
@@ -8083,7 +8113,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>223</v>
@@ -8094,7 +8124,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>276</v>
@@ -8105,7 +8135,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>345</v>
@@ -8116,7 +8146,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>279</v>
@@ -8127,7 +8157,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>159</v>
@@ -8138,7 +8168,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>175</v>
@@ -8149,7 +8179,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>225</v>
@@ -8160,7 +8190,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>222</v>
@@ -8171,7 +8201,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>226</v>
@@ -8182,7 +8212,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>278</v>
@@ -8193,7 +8223,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>339</v>

--- a/QuanLyNhaHang.xlsx
+++ b/QuanLyNhaHang.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMINIS\Documents\QuanLyDatMonNhaHang\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐỒ ÁN IT008\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199CC3CD-0F83-459E-B135-57F53584852B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6755FA-4F43-4D30-9ABB-85C5C9166C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{54FD8D7C-BB94-496C-BA96-0560A95F9D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="KhachHang" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="766">
   <si>
     <t>MaKH</t>
   </si>
@@ -184,34 +184,7 @@
     <t>B10</t>
   </si>
   <si>
-    <t>2023-07-01</t>
-  </si>
-  <si>
-    <t>2023-07-15</t>
-  </si>
-  <si>
     <t>Đã thanh toán</t>
-  </si>
-  <si>
-    <t>2023-07-22</t>
-  </si>
-  <si>
-    <t>2023-07-29</t>
-  </si>
-  <si>
-    <t>2023-08-05</t>
-  </si>
-  <si>
-    <t>2023-08-12</t>
-  </si>
-  <si>
-    <t>2023-08-19</t>
-  </si>
-  <si>
-    <t>2023-08-26</t>
-  </si>
-  <si>
-    <t>2023-09-02</t>
   </si>
   <si>
     <t>L01</t>
@@ -2333,14 +2306,48 @@
   <si>
     <t>Súp hải sản, Cuốn diếp tôm thịt, Sườn cừu nướng sốt rượu vang đỏ, Vịt quay sốt cam, Cá hồi áp chảo sốt bơ chanh, Lẩu Nấm Truffle Kem Sữa, Chè khúc bạch
 5-8 người</t>
+  </si>
+  <si>
+    <t>HD011</t>
+  </si>
+  <si>
+    <t>HD012</t>
+  </si>
+  <si>
+    <t>HD013</t>
+  </si>
+  <si>
+    <t>HD014</t>
+  </si>
+  <si>
+    <t>HD015</t>
+  </si>
+  <si>
+    <t>HD016</t>
+  </si>
+  <si>
+    <t>HD017</t>
+  </si>
+  <si>
+    <t>HD018</t>
+  </si>
+  <si>
+    <t>HD019</t>
+  </si>
+  <si>
+    <t>HD020</t>
+  </si>
+  <si>
+    <t>HD021</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-1000000]h:mm:ss;@"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -2512,7 +2519,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2612,6 +2619,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3219,328 +3233,328 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C3" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -3576,10 +3590,10 @@
         <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>14</v>
@@ -3590,2954 +3604,2954 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="G2" s="6">
         <v>75000</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="G3" s="6">
         <v>125000</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="G4" s="6">
         <v>65000</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="G5" s="6">
         <v>80000</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="G6" s="6">
         <v>95000</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="G7" s="6">
         <v>90000</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="G8" s="6">
         <v>145000</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="G9" s="6">
         <v>120000</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="G10" s="6">
         <v>135000</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="G11" s="6">
         <v>100000</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="G12" s="6">
         <v>150000</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="G13" s="6">
         <v>100000</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="G14" s="6">
         <v>130000</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="G15" s="6">
         <v>90000</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="G16" s="6">
         <v>120000</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="G17" s="6">
         <v>95000</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="G18" s="6">
         <v>110000</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="G19" s="6">
         <v>95000</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="G20" s="6">
         <v>100000</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="G21" s="6">
         <v>85000</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="G22" s="7">
         <v>135000</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="G23" s="7">
         <v>220000</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="G24" s="7">
         <v>120000</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="G25" s="7">
         <v>140000</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="G26" s="7">
         <v>180000</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="G27" s="7">
         <v>210000</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="G28" s="7">
         <v>190000</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="G29" s="7">
         <v>175000</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="G30" s="7">
         <v>200000</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="G31" s="7">
         <v>110000</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="G32" s="7">
         <v>95000</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="G33" s="7">
         <v>85000</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="G34" s="7">
         <v>90000</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="G35" s="7">
         <v>130000</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="G36" s="7">
         <v>100000</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="G37" s="7">
         <v>250000</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="G38" s="7">
         <v>270000</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="G39" s="7">
         <v>230000</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="G40" s="7">
         <v>290000</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="G41" s="7">
         <v>280000</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="G42" s="7">
         <v>240000</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="G43" s="7">
         <v>300000</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="G44" s="7">
         <v>190000</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="G45" s="7">
         <v>195000</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="G46" s="7">
         <v>350000</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="G47" s="7">
         <v>330000</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="F48" s="28" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="G48" s="7">
         <v>379000</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="F49" s="32" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="G49" s="16">
         <v>500000</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="G50" s="17">
         <v>79000</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="F51" s="28" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="G51" s="17">
         <v>69000</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D52" s="30" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="E52" s="28" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="F52" s="28" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="G52" s="17">
         <v>59000</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="G53" s="17">
         <v>69000</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E54" s="28" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="G54" s="14">
         <v>55000</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="G55" s="17">
         <v>45000</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="F56" s="28" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="G56" s="17">
         <v>59000</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="G57" s="17">
         <v>65000</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="F58" s="28" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="G58" s="17">
         <v>79000</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="G59" s="17">
         <v>69000</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="F60" s="28" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="G60" s="14">
         <v>65000</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="F61" s="28" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="G61" s="17">
         <v>45000</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="D62" s="30" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="F62" s="28" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="G62" s="17">
         <v>69000</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="F63" s="28" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="G63" s="17">
         <v>55000</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="E64" s="28" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="F64" s="28" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="G64" s="14">
         <v>49000</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="F65" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G65" s="6">
         <v>60000</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="F66" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G66" s="6">
         <v>65000</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="E67" s="32" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G67" s="6">
         <v>45000</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F68" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G68" s="6">
         <v>55000</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="F69" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G69" s="6">
         <v>40000</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="F70" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G70" s="6">
         <v>45000</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="F71" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G71" s="6">
         <v>38000</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="F72" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G72" s="6">
         <v>20000</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="F73" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G73" s="6">
         <v>30000</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="E74" s="28" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="F74" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G74" s="6">
         <v>30000</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="E75" s="28" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="F75" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G75" s="6">
         <v>30000</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="D76" s="26" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="F76" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G76" s="6">
         <v>30000</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="E77" s="28" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F77" s="28" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="G77" s="6">
         <v>160000</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="E78" s="28" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F78" s="28" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="G78" s="6">
         <v>180000</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="E79" s="28" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F79" s="28" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="G79" s="6">
         <v>170000</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D80" s="26" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="E80" s="28" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F80" s="28" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="G80" s="6">
         <v>220000</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D81" s="26" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G81" s="6">
         <v>100000</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="D82" s="26" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="F82" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G82" s="6">
         <v>90000</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E83" s="28" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="F83" s="28" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G83" s="6">
         <v>85000</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="D84" s="26" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E84" s="28" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="F84" s="28" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="G84" s="6">
         <v>130000</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="E85" s="28" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="F85" s="28" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="G85" s="6">
         <v>125000</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="F86" s="28" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="G86" s="6">
         <v>200000</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="D87" s="26" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="G87" s="6">
         <v>30000</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="F88" s="28" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="G88" s="18">
         <v>35000</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="D89" s="26" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="F89" s="28" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="G89" s="6">
         <v>70000</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B90" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="D90" s="30" t="s">
         <v>458</v>
       </c>
-      <c r="C90" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="D90" s="30" t="s">
-        <v>467</v>
-      </c>
       <c r="E90" s="28" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="F90" s="28" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="G90" s="6">
         <v>25000</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D91" s="26" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="G91" s="6">
         <v>70000</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="E92" s="28" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="F92" s="28" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="G92" s="6">
         <v>85000</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="D93" s="30" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="E93" s="28" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="F93" s="28" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="G93" s="18">
         <v>60000</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="B94" s="20" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="D94" s="31" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="G94" s="9">
         <v>45000</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="D95" s="26" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E95" s="28" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="F95" s="28" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="G95" s="6">
         <v>50000</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="D96" s="30" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="F96" s="28" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="G96" s="6">
         <v>65000</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="D97" s="26" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="E97" s="28" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="F97" s="28" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="G97" s="6">
         <v>50000</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B98" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="D98" s="26" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="11" t="s">
-        <v>551</v>
-      </c>
-      <c r="D98" s="26" t="s">
-        <v>489</v>
-      </c>
       <c r="E98" s="28" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="F98" s="28" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="G98" s="6">
         <v>55000</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="D99" s="26" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="E99" s="28" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="F99" s="28" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="G99" s="6">
         <v>65000</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="D100" s="26" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="E100" s="28" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="F100" s="28" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="G100" s="6">
         <v>85000</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="D101" s="26" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="F101" s="28" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="G101" s="17">
         <v>5000</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="D102" s="30" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="F102" s="28" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="G102" s="17">
         <v>8000</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="F103" s="28" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="G103" s="14">
         <v>15000</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="D104" s="26" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="F104" s="28" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="G104" s="14">
         <v>12000</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="D105" s="26" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="F105" s="28" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="G105" s="14">
         <v>10000</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="D106" s="26" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="E106" s="28" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="F106" s="28" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="G106" s="14">
         <v>10000</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="E107" s="28" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="F107" s="28" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="G107" s="14">
         <v>8000</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="D108" s="26" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="E108" s="28" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="F108" s="28" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="G108" s="17">
         <v>12000</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="F109" s="28" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="G109" s="17">
         <v>10000</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="D110" s="26" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="F110" s="28" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="G110" s="17">
         <v>10000</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="D111" s="26" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="E111" s="28" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="F111" s="28" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="G111" s="17">
         <v>8000</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="E112" s="28" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="F112" s="28" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="G112" s="17">
         <v>12000</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="D113" s="30" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="F113" s="28" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="G113" s="17">
         <v>12000</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="D114" s="30" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E114" s="28" t="s">
+        <v>723</v>
+      </c>
+      <c r="F114" s="28" t="s">
         <v>732</v>
-      </c>
-      <c r="F114" s="28" t="s">
-        <v>741</v>
       </c>
       <c r="G114" s="17">
         <v>15000</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="D115" s="30" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="E115" s="28"/>
       <c r="F115" s="28"/>
@@ -6545,21 +6559,21 @@
         <v>503000</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="D116" s="34" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="E116" s="28"/>
       <c r="F116" s="28"/>
@@ -6567,21 +6581,21 @@
         <v>503000</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="D117" s="34" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="E117" s="28"/>
       <c r="F117" s="28"/>
@@ -6589,21 +6603,21 @@
         <v>665000</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="D118" s="34" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="E118" s="28"/>
       <c r="F118" s="28"/>
@@ -6611,21 +6625,21 @@
         <v>840000</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="D119" s="34" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="E119" s="28"/>
       <c r="F119" s="28"/>
@@ -6633,21 +6647,21 @@
         <v>970000</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="D120" s="34" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="E120" s="28"/>
       <c r="F120" s="28"/>
@@ -6655,21 +6669,21 @@
         <v>927000</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="D121" s="34" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="E121" s="28"/>
       <c r="F121" s="28"/>
@@ -6677,21 +6691,21 @@
         <v>1537000</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="D122" s="34" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="E122" s="28"/>
       <c r="F122" s="28"/>
@@ -6699,21 +6713,21 @@
         <v>1470000</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="D123" s="34" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="E123" s="28"/>
       <c r="F123" s="28"/>
@@ -6721,7 +6735,7 @@
         <v>1912000</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -6733,13 +6747,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C67116-806E-4F8F-AE20-17E61EFDB4E5}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.88671875" customWidth="1"/>
     <col min="4" max="4" width="14.88671875" customWidth="1"/>
     <col min="5" max="5" width="19.109375" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" customWidth="1"/>
+    <col min="6" max="6" width="20.88671875" style="37" customWidth="1"/>
     <col min="7" max="7" width="16.21875" customWidth="1"/>
     <col min="8" max="8" width="14.44140625" customWidth="1"/>
     <col min="9" max="9" width="20.6640625" customWidth="1"/>
@@ -6758,19 +6772,19 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="F1" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="F1" s="35" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
@@ -6781,7 +6795,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>47</v>
@@ -6790,13 +6804,13 @@
         <v>31</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>589</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>50</v>
+        <v>580</v>
+      </c>
+      <c r="F2" s="36">
+        <v>45839</v>
       </c>
       <c r="G2" s="7">
         <v>585000</v>
@@ -6808,12 +6822,12 @@
         <v>580745</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>39</v>
@@ -6822,13 +6836,13 @@
         <v>23</v>
       </c>
       <c r="D3" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>590</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>599</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>34</v>
+      <c r="F3" s="36">
+        <v>45846</v>
       </c>
       <c r="G3" s="7">
         <v>270000</v>
@@ -6840,12 +6854,12 @@
         <v>250000</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>41</v>
@@ -6854,13 +6868,13 @@
         <v>23</v>
       </c>
       <c r="D4" s="21" t="s">
+        <v>582</v>
+      </c>
+      <c r="E4" s="21" t="s">
         <v>591</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>600</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>51</v>
+      <c r="F4" s="36">
+        <v>45853</v>
       </c>
       <c r="G4" s="7">
         <v>890000</v>
@@ -6872,12 +6886,12 @@
         <v>890000</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -6886,13 +6900,13 @@
         <v>25</v>
       </c>
       <c r="D5" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>592</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>601</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>53</v>
+      <c r="F5" s="36">
+        <v>45860</v>
       </c>
       <c r="G5" s="7">
         <v>230000</v>
@@ -6904,12 +6918,12 @@
         <v>230000</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>43</v>
@@ -6918,13 +6932,13 @@
         <v>27</v>
       </c>
       <c r="D6" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>593</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>602</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>54</v>
+      <c r="F6" s="36">
+        <v>45867</v>
       </c>
       <c r="G6" s="7">
         <v>1070000</v>
@@ -6936,12 +6950,12 @@
         <v>1060500</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>48</v>
@@ -6950,13 +6964,13 @@
         <v>21</v>
       </c>
       <c r="D7" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="E7" s="21" t="s">
         <v>594</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>603</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>55</v>
+      <c r="F7" s="36">
+        <v>45874</v>
       </c>
       <c r="G7" s="7">
         <v>215000</v>
@@ -6968,12 +6982,12 @@
         <v>215000</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>43</v>
@@ -6982,13 +6996,13 @@
         <v>33</v>
       </c>
       <c r="D8" s="21" t="s">
+        <v>586</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>595</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>604</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>56</v>
+      <c r="F8" s="36">
+        <v>45881</v>
       </c>
       <c r="G8" s="7">
         <v>1680000</v>
@@ -7000,12 +7014,12 @@
         <v>1680000</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>39</v>
@@ -7014,13 +7028,13 @@
         <v>21</v>
       </c>
       <c r="D9" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>596</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>605</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>57</v>
+      <c r="F9" s="36">
+        <v>45888</v>
       </c>
       <c r="G9" s="7">
         <v>915000</v>
@@ -7032,12 +7046,12 @@
         <v>912000</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>48</v>
@@ -7046,13 +7060,13 @@
         <v>33</v>
       </c>
       <c r="D10" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="E10" s="21" t="s">
         <v>597</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>606</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>58</v>
+      <c r="F10" s="36">
+        <v>45895</v>
       </c>
       <c r="G10" s="7">
         <v>260000</v>
@@ -7064,12 +7078,12 @@
         <v>248000</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>49</v>
@@ -7078,13 +7092,13 @@
         <v>21</v>
       </c>
       <c r="D11" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>598</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>607</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>59</v>
+      <c r="F11" s="36">
+        <v>45902</v>
       </c>
       <c r="G11" s="7">
         <v>465000</v>
@@ -7096,7 +7110,359 @@
         <v>456000</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>755</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="F12" s="36">
+        <v>45922</v>
+      </c>
+      <c r="G12" s="7">
+        <v>230000</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
+      <c r="I12" s="7">
+        <v>230000</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="F13" s="36">
+        <v>45929</v>
+      </c>
+      <c r="G13" s="7">
+        <v>1070000</v>
+      </c>
+      <c r="H13" s="7">
+        <v>9500</v>
+      </c>
+      <c r="I13" s="7">
+        <v>1060500</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>594</v>
+      </c>
+      <c r="F14" s="36">
+        <v>45931</v>
+      </c>
+      <c r="G14" s="7">
+        <v>215000</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7">
+        <v>215000</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>579</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>580</v>
+      </c>
+      <c r="F15" s="36">
+        <v>45935</v>
+      </c>
+      <c r="G15" s="7">
+        <v>585000</v>
+      </c>
+      <c r="H15" s="7">
+        <v>4255</v>
+      </c>
+      <c r="I15" s="7">
+        <v>580745</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="F16" s="36">
+        <v>45938</v>
+      </c>
+      <c r="G16" s="7">
+        <v>270000</v>
+      </c>
+      <c r="H16" s="7">
+        <v>15000</v>
+      </c>
+      <c r="I16" s="7">
+        <v>250000</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>582</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>591</v>
+      </c>
+      <c r="F17" s="36">
+        <v>45976</v>
+      </c>
+      <c r="G17" s="7">
+        <v>890000</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7">
+        <v>890000</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="F18" s="36">
+        <v>45983</v>
+      </c>
+      <c r="G18" s="7">
+        <v>230000</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7">
+        <v>230000</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="F19" s="36">
+        <v>45993</v>
+      </c>
+      <c r="G19" s="7">
+        <v>915000</v>
+      </c>
+      <c r="H19" s="7">
+        <v>3000</v>
+      </c>
+      <c r="I19" s="7">
+        <v>912000</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="F20" s="36">
+        <v>46002</v>
+      </c>
+      <c r="G20" s="7">
+        <v>260000</v>
+      </c>
+      <c r="H20" s="7">
+        <v>12000</v>
+      </c>
+      <c r="I20" s="7">
+        <v>248000</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="F21" s="36">
+        <v>46013</v>
+      </c>
+      <c r="G21" s="7">
+        <v>465000</v>
+      </c>
+      <c r="H21" s="7">
+        <v>9000</v>
+      </c>
+      <c r="I21" s="7">
+        <v>456000</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="F22" s="36">
+        <v>46017</v>
+      </c>
+      <c r="G22" s="7">
+        <v>230000</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0</v>
+      </c>
+      <c r="I22" s="7">
+        <v>230000</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -7119,21 +7485,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="B2" s="33">
         <v>50</v>
@@ -7147,7 +7513,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="B3" s="33">
         <v>400</v>
@@ -7161,7 +7527,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="B4" s="33">
         <v>750</v>
@@ -7175,7 +7541,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="B5" s="33">
         <v>150</v>
@@ -7189,7 +7555,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="B6" s="33">
         <v>3000</v>
@@ -7208,7 +7574,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FC086EC-74CB-4344-93F9-D1F3265B5BB1}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="4" width="9.88671875" customWidth="1"/>
@@ -7226,7 +7592,7 @@
         <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -7234,10 +7600,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C2" s="6">
         <v>2</v>
@@ -7251,10 +7617,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -7268,10 +7634,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C4" s="6">
         <v>2</v>
@@ -7285,10 +7651,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
@@ -7302,10 +7668,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -7319,10 +7685,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -7336,10 +7702,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C8" s="6">
         <v>2</v>
@@ -7353,10 +7719,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -7370,10 +7736,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C10" s="6">
         <v>3</v>
@@ -7387,10 +7753,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -7404,10 +7770,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -7421,10 +7787,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C13" s="6">
         <v>2</v>
@@ -7438,10 +7804,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C14" s="6">
         <v>4</v>
@@ -7455,10 +7821,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -7472,10 +7838,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
@@ -7489,10 +7855,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="C17" s="6">
         <v>2</v>
@@ -7506,10 +7872,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
@@ -7523,10 +7889,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C19" s="6">
         <v>1</v>
@@ -7540,10 +7906,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C20" s="6">
         <v>2</v>
@@ -7557,10 +7923,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C21" s="6">
         <v>2</v>
@@ -7574,10 +7940,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
@@ -7591,10 +7957,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
@@ -7608,10 +7974,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C24" s="6">
         <v>1</v>
@@ -7623,7 +7989,450 @@
         <v>135000</v>
       </c>
     </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6">
+        <v>80000</v>
+      </c>
+      <c r="E25" s="6">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6">
+        <v>150000</v>
+      </c>
+      <c r="E26" s="6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2</v>
+      </c>
+      <c r="D27" s="6">
+        <v>95000</v>
+      </c>
+      <c r="E27" s="6">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="6">
+        <v>4</v>
+      </c>
+      <c r="D28" s="6">
+        <v>220000</v>
+      </c>
+      <c r="E28" s="6">
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1</v>
+      </c>
+      <c r="D29" s="6">
+        <v>65000</v>
+      </c>
+      <c r="E29" s="6">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6">
+        <v>150000</v>
+      </c>
+      <c r="E30" s="6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" s="6">
+        <v>2</v>
+      </c>
+      <c r="D31" s="6">
+        <v>125000</v>
+      </c>
+      <c r="E31" s="6">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6">
+        <v>95000</v>
+      </c>
+      <c r="E32" s="6">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C33" s="6">
+        <v>2</v>
+      </c>
+      <c r="D33" s="6">
+        <v>120000</v>
+      </c>
+      <c r="E33" s="6">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
+      <c r="D34" s="6">
+        <v>90000</v>
+      </c>
+      <c r="E34" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1</v>
+      </c>
+      <c r="D35" s="6">
+        <v>180000</v>
+      </c>
+      <c r="E35" s="6">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="6">
+        <v>1</v>
+      </c>
+      <c r="D36" s="6">
+        <v>75000</v>
+      </c>
+      <c r="E36" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" s="6">
+        <v>2</v>
+      </c>
+      <c r="D37" s="6">
+        <v>130000</v>
+      </c>
+      <c r="E37" s="6">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1</v>
+      </c>
+      <c r="D38" s="6">
+        <v>135000</v>
+      </c>
+      <c r="E38" s="6">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" s="6">
+        <v>3</v>
+      </c>
+      <c r="D39" s="6">
+        <v>140000</v>
+      </c>
+      <c r="E39" s="6">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" s="6">
+        <v>1</v>
+      </c>
+      <c r="D40" s="6">
+        <v>80000</v>
+      </c>
+      <c r="E40" s="6">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1</v>
+      </c>
+      <c r="D41" s="6">
+        <v>150000</v>
+      </c>
+      <c r="E41" s="6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1</v>
+      </c>
+      <c r="D42" s="6">
+        <v>125000</v>
+      </c>
+      <c r="E42" s="6">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" s="6">
+        <v>1</v>
+      </c>
+      <c r="D43" s="6">
+        <v>190000</v>
+      </c>
+      <c r="E43" s="6">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C44" s="6">
+        <v>2</v>
+      </c>
+      <c r="D44" s="6">
+        <v>300000</v>
+      </c>
+      <c r="E44" s="6">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45" s="6">
+        <v>2</v>
+      </c>
+      <c r="D45" s="6">
+        <v>130000</v>
+      </c>
+      <c r="E45" s="6">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="6">
+        <v>1</v>
+      </c>
+      <c r="D46" s="6">
+        <v>90000</v>
+      </c>
+      <c r="E46" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1</v>
+      </c>
+      <c r="D47" s="22">
+        <v>240000</v>
+      </c>
+      <c r="E47" s="6">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" s="6">
+        <v>1</v>
+      </c>
+      <c r="D48" s="6">
+        <v>135000</v>
+      </c>
+      <c r="E48" s="6">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C49" s="6">
+        <v>1</v>
+      </c>
+      <c r="D49" s="6">
+        <v>80000</v>
+      </c>
+      <c r="E49" s="6">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" s="6">
+        <v>1</v>
+      </c>
+      <c r="D50" s="6">
+        <v>150000</v>
+      </c>
+      <c r="E50" s="6">
+        <v>150000</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7651,10 +8460,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
@@ -7662,10 +8471,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -7673,10 +8482,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
@@ -7684,10 +8493,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
@@ -7695,10 +8504,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -7706,10 +8515,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -7717,10 +8526,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
@@ -7728,10 +8537,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -7739,10 +8548,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
@@ -7750,10 +8559,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -7761,10 +8570,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -7772,10 +8581,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -7783,10 +8592,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C14" s="6">
         <v>1</v>
@@ -7794,10 +8603,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -7805,10 +8614,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
@@ -7816,10 +8625,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C17" s="6">
         <v>1</v>
@@ -7827,10 +8636,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
@@ -7838,10 +8647,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C19" s="6">
         <v>2</v>
@@ -7849,10 +8658,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
@@ -7860,10 +8669,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C21" s="6">
         <v>1</v>
@@ -7871,10 +8680,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
@@ -7882,10 +8691,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
@@ -7893,10 +8702,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C24" s="6">
         <v>1</v>
@@ -7904,10 +8713,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C25" s="6">
         <v>2</v>
@@ -7915,10 +8724,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C26" s="6">
         <v>1</v>
@@ -7926,10 +8735,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C27" s="6">
         <v>1</v>
@@ -7937,10 +8746,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C28" s="6">
         <v>1</v>
@@ -7948,10 +8757,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C29" s="6">
         <v>1</v>
@@ -7959,10 +8768,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C30" s="6">
         <v>1</v>
@@ -7970,10 +8779,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C31" s="6">
         <v>2</v>
@@ -7981,10 +8790,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C32" s="6">
         <v>2</v>
@@ -7992,10 +8801,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C33" s="6">
         <v>2</v>
@@ -8003,10 +8812,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C34" s="6">
         <v>1</v>
@@ -8014,10 +8823,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C35" s="6">
         <v>2</v>
@@ -8025,10 +8834,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C36" s="6">
         <v>1</v>
@@ -8036,10 +8845,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C37" s="6">
         <v>1</v>
@@ -8047,10 +8856,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C38" s="6">
         <v>2</v>
@@ -8058,10 +8867,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C39" s="6">
         <v>1</v>
@@ -8069,10 +8878,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C40" s="6">
         <v>2</v>
@@ -8080,10 +8889,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C41" s="6">
         <v>2</v>
@@ -8091,10 +8900,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C42" s="6">
         <v>2</v>
@@ -8102,10 +8911,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C43" s="6">
         <v>1</v>
@@ -8113,10 +8922,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C44" s="6">
         <v>1</v>
@@ -8124,10 +8933,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C45" s="6">
         <v>1</v>
@@ -8135,10 +8944,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C46" s="6">
         <v>2</v>
@@ -8146,10 +8955,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C47" s="6">
         <v>1</v>
@@ -8157,10 +8966,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C48" s="6">
         <v>2</v>
@@ -8168,10 +8977,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C49" s="6">
         <v>2</v>
@@ -8179,10 +8988,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -8190,10 +8999,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C51" s="6">
         <v>1</v>
@@ -8201,10 +9010,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C52" s="6">
         <v>2</v>
@@ -8212,10 +9021,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C53" s="6">
         <v>1</v>
@@ -8223,10 +9032,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C54" s="6">
         <v>2</v>
